--- a/ups_requests.xlsx
+++ b/ups_requests.xlsx
@@ -42263,7 +42263,7 @@
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1136" t="inlineStr">
@@ -46736,7 +46736,7 @@
       </c>
       <c r="F1257" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1257" t="inlineStr">
@@ -47661,7 +47661,7 @@
       </c>
       <c r="F1282" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1282" t="inlineStr">
@@ -48031,7 +48031,7 @@
       </c>
       <c r="F1292" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1292" t="inlineStr">
@@ -49844,7 +49844,7 @@
       </c>
       <c r="F1341" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1341" t="inlineStr">
@@ -51398,7 +51398,7 @@
       </c>
       <c r="F1383" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1383" t="inlineStr">
@@ -51649,7 +51649,7 @@
       </c>
       <c r="F1390" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1390" t="inlineStr">
@@ -52204,7 +52204,7 @@
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1405" t="inlineStr">

--- a/ups_requests.xlsx
+++ b/ups_requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1540"/>
+  <dimension ref="A1:G1566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -32499,7 +32499,7 @@
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G872" t="inlineStr">
@@ -35825,7 +35825,7 @@
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G962" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G988" t="inlineStr">
@@ -39673,7 +39673,7 @@
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1066" t="inlineStr">
@@ -41190,7 +41190,7 @@
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1107" t="inlineStr">
@@ -42263,7 +42263,7 @@
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1136" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="F1151" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1151" t="inlineStr">
@@ -43558,7 +43558,7 @@
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1171" t="inlineStr">
@@ -43595,7 +43595,7 @@
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1172" t="inlineStr">
@@ -43632,7 +43632,7 @@
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1173" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1175" t="inlineStr">
@@ -43817,7 +43817,7 @@
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1178" t="inlineStr">
@@ -44368,7 +44368,7 @@
       </c>
       <c r="F1193" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1193" t="inlineStr">
@@ -45219,7 +45219,7 @@
       </c>
       <c r="F1216" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1216" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="F1252" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1252" t="inlineStr">
@@ -46736,7 +46736,7 @@
       </c>
       <c r="F1257" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1257" t="inlineStr">
@@ -47143,7 +47143,7 @@
       </c>
       <c r="F1268" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1268" t="inlineStr">
@@ -47661,7 +47661,7 @@
       </c>
       <c r="F1282" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1282" t="inlineStr">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="F1315" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1315" t="inlineStr">
@@ -49067,7 +49067,7 @@
       </c>
       <c r="F1320" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1320" t="inlineStr">
@@ -49511,7 +49511,7 @@
       </c>
       <c r="F1332" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1332" t="inlineStr">
@@ -50066,7 +50066,7 @@
       </c>
       <c r="F1347" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1347" t="inlineStr">
@@ -50103,7 +50103,7 @@
       </c>
       <c r="F1348" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1348" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="F1349" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1349" t="inlineStr">
@@ -51176,7 +51176,7 @@
       </c>
       <c r="F1377" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1377" t="inlineStr">
@@ -51361,7 +51361,7 @@
       </c>
       <c r="F1382" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1382" t="inlineStr">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="F1388" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1388" t="inlineStr">
@@ -51624,12 +51624,12 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>BLS-LR269360</t>
+          <t>BLS-LR269359</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>20268276</t>
+          <t>20268429</t>
         </is>
       </c>
       <c r="C1390" t="inlineStr">
@@ -51661,12 +51661,12 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>BLS-LR269361</t>
+          <t>BLS-LR269360</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>20268240</t>
+          <t>20268276</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr">
@@ -51676,7 +51676,7 @@
       </c>
       <c r="D1391" t="inlineStr">
         <is>
-          <t>شجاع راشد بن محمد القحطانى</t>
+          <t>محمد احمد محمد القحطاني</t>
         </is>
       </c>
       <c r="E1391" t="inlineStr">
@@ -51686,7 +51686,7 @@
       </c>
       <c r="F1391" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1391" t="inlineStr">
@@ -51698,12 +51698,12 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>BLS-LR269367</t>
+          <t>BLS-LR269361</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>20268247</t>
+          <t>20268240</t>
         </is>
       </c>
       <c r="C1392" t="inlineStr">
@@ -51713,17 +51713,17 @@
       </c>
       <c r="D1392" t="inlineStr">
         <is>
-          <t>شركة الأفق الشمالي للتطوير العقاري</t>
+          <t>شجاع راشد بن محمد القحطانى</t>
         </is>
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1392" t="inlineStr">
@@ -51735,32 +51735,32 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>BLS-LR26937</t>
+          <t>BLS-LR269367</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>2026817</t>
+          <t>20268247</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1393" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>شركة الأفق الشمالي للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1393" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1393" t="inlineStr">
@@ -51772,32 +51772,32 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>BLS-LR269372</t>
+          <t>BLS-LR26937</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>20268254</t>
+          <t>2026817</t>
         </is>
       </c>
       <c r="C1394" t="inlineStr">
         <is>
-          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1394" t="inlineStr">
         <is>
-          <t>محمد احمد محمد القحطاني</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1394" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1394" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1394" t="inlineStr">
@@ -51809,12 +51809,12 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>BLS-LR269386</t>
+          <t>BLS-LR269372</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>20268274</t>
+          <t>20268254</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr">
@@ -51824,12 +51824,12 @@
       </c>
       <c r="D1395" t="inlineStr">
         <is>
-          <t>ابراهيم بن عبدالله بن موسى الحمودي</t>
+          <t>محمد احمد محمد القحطاني</t>
         </is>
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1395" t="inlineStr">
@@ -51846,12 +51846,12 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>BLS-LR269392</t>
+          <t>BLS-LR269386</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>20268268</t>
+          <t>20268274</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr">
@@ -51861,17 +51861,17 @@
       </c>
       <c r="D1396" t="inlineStr">
         <is>
-          <t>عبدالله بن شباب بن عيد العصيمي</t>
+          <t>ابراهيم بن عبدالله بن موسى الحمودي</t>
         </is>
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1396" t="inlineStr">
@@ -51883,22 +51883,22 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>BLS-LR2694</t>
+          <t>BLS-LR269392</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>202695</t>
+          <t>20268268</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>٧ - شعبان - ١٤٤٧ هـ</t>
+          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1397" t="inlineStr">
         <is>
-          <t>شركة ألوينر ريزيدنس</t>
+          <t>عبدالله بن شباب بن عيد العصيمي</t>
         </is>
       </c>
       <c r="E1397" t="inlineStr">
@@ -51908,7 +51908,7 @@
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
@@ -51920,27 +51920,27 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>BLS-LR269415</t>
+          <t>BLS-LR2694</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>20268292</t>
+          <t>202695</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٧ - شعبان - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1398" t="inlineStr">
         <is>
-          <t>محمد عبيد علي القحطاني</t>
+          <t>شركة ألوينر ريزيدنس</t>
         </is>
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1398" t="inlineStr">
@@ -51957,32 +51957,32 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>BLS-LR26943</t>
+          <t>BLS-LR269415</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>2026829</t>
+          <t>20268292</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1399" t="inlineStr">
         <is>
-          <t>علي سعيد بن صنيتان المطيري</t>
+          <t>محمد عبيد علي القحطاني</t>
         </is>
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1399" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1399" t="inlineStr">
@@ -51994,12 +51994,12 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>BLS-LR269444</t>
+          <t>BLS-LR269418</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>20268324</t>
+          <t>20268471</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr">
@@ -52009,12 +52009,12 @@
       </c>
       <c r="D1400" t="inlineStr">
         <is>
-          <t>مؤسسة مشارف المنزل للتجارة</t>
+          <t>عبدالله محمد احمد القرني</t>
         </is>
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1400" t="inlineStr">
@@ -52031,32 +52031,32 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>BLS-LR269447</t>
+          <t>BLS-LR26943</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>20268316</t>
+          <t>2026829</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1401" t="inlineStr">
         <is>
-          <t>شركة مدينة الضباب للتطوير العقاري</t>
+          <t>علي سعيد بن صنيتان المطيري</t>
         </is>
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1401" t="inlineStr">
@@ -52068,32 +52068,32 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>BLS-LR26945</t>
+          <t>BLS-LR269444</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>2026950</t>
+          <t>20268324</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr">
         <is>
-          <t>ناصر عبدالله حجيلان الشيباني</t>
+          <t>مؤسسة مشارف المنزل للتجارة</t>
         </is>
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1402" t="inlineStr">
@@ -52105,12 +52105,12 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>BLS-LR269453</t>
+          <t>BLS-LR269447</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>20268319</t>
+          <t>20268316</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr">
@@ -52120,17 +52120,17 @@
       </c>
       <c r="D1403" t="inlineStr">
         <is>
-          <t>علي محمد علي الأسمري</t>
+          <t>شركة مدينة الضباب للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1403" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1403" t="inlineStr">
@@ -52142,12 +52142,12 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>BLS-LR26946</t>
+          <t>BLS-LR26945</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>2026824</t>
+          <t>2026950</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr">
@@ -52157,12 +52157,12 @@
       </c>
       <c r="D1404" t="inlineStr">
         <is>
-          <t>سلطان مبارك بن مفلح القحطاني</t>
+          <t>ناصر عبدالله حجيلان الشيباني</t>
         </is>
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1404" t="inlineStr">
@@ -52179,27 +52179,27 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>BLS-LR269476</t>
+          <t>BLS-LR269453</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>20268371</t>
+          <t>20268319</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1405" t="inlineStr">
         <is>
-          <t>وائل فائز رفدان الدوسري</t>
+          <t>علي محمد علي الأسمري</t>
         </is>
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1405" t="inlineStr">
@@ -52216,12 +52216,12 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>BLS-LR26949</t>
+          <t>BLS-LR26946</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>2026827</t>
+          <t>2026824</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr">
@@ -52253,12 +52253,12 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>BLS-LR269495</t>
+          <t>BLS-LR269476</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>20268370</t>
+          <t>20268371</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
@@ -52268,17 +52268,17 @@
       </c>
       <c r="D1407" t="inlineStr">
         <is>
-          <t>مؤسسة وهج الجوهرة للتطوير والاستثمار العقاري</t>
+          <t>وائل فائز رفدان الدوسري</t>
         </is>
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1407" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1407" t="inlineStr">
@@ -52290,12 +52290,12 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>BLS-LR26950</t>
+          <t>BLS-LR26949</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>2026830</t>
+          <t>2026827</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr">
@@ -52305,17 +52305,17 @@
       </c>
       <c r="D1408" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>سلطان مبارك بن مفلح القحطاني</t>
         </is>
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1408" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1408" t="inlineStr">
@@ -52327,12 +52327,12 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>BLS-LR269507</t>
+          <t>BLS-LR269495</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>20268367</t>
+          <t>20268370</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
@@ -52342,17 +52342,17 @@
       </c>
       <c r="D1409" t="inlineStr">
         <is>
-          <t>رشيد عبدالله سعيد السملق</t>
+          <t>مؤسسة وهج الجوهرة للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1409" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1409" t="inlineStr">
@@ -52364,12 +52364,12 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>BLS-LR26951</t>
+          <t>BLS-LR26950</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>2026832</t>
+          <t>2026830</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr">
@@ -52379,17 +52379,17 @@
       </c>
       <c r="D1410" t="inlineStr">
         <is>
-          <t>ذعار عايض ذعار العجمي</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1410" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1410" t="inlineStr">
@@ -52401,32 +52401,32 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>BLS-LR26955</t>
+          <t>BLS-LR269500</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>20261076</t>
+          <t>20268413</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr">
         <is>
-          <t>عبير عبدالعزيز عبدالله الصالح</t>
+          <t>مسفر صالح عبدالله الدوسري</t>
         </is>
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1411" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1411" t="inlineStr">
@@ -52438,32 +52438,32 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>BLS-LR26958</t>
+          <t>BLS-LR269507</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>2026836</t>
+          <t>20268367</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
         <is>
-          <t>ذعار عايض ذعار العجمي</t>
+          <t>رشيد عبدالله سعيد السملق</t>
         </is>
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1412" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1412" t="inlineStr">
@@ -52475,32 +52475,32 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>BLS-LR26968</t>
+          <t>BLS-LR26951</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>20261517</t>
+          <t>2026832</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr">
         <is>
-          <t>حراز سعيد عايض العتيبي</t>
+          <t>ذعار عايض ذعار العجمي</t>
         </is>
       </c>
       <c r="E1413" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1413" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1413" t="inlineStr">
@@ -52512,32 +52512,32 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>BLS-LR26969</t>
+          <t>BLS-LR269544</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>2026858</t>
+          <t>20268414</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr">
         <is>
-          <t>مؤسسة شوق حميد المطيري للتطوير العقاري</t>
+          <t>مؤسسة مبارك عبدالله بن مبارك آل مغيره للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1414" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1414" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1414" t="inlineStr">
@@ -52549,32 +52549,32 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>BLS-LR26971</t>
+          <t>BLS-LR269547</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>20261495</t>
+          <t>20268421</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr">
         <is>
-          <t>مؤسسة قدم العقارية</t>
+          <t>شركة استدامة الأعمال المالية</t>
         </is>
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره البديعه</t>
         </is>
       </c>
       <c r="F1415" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1415" t="inlineStr">
@@ -52586,12 +52586,12 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>BLS-LR26972</t>
+          <t>BLS-LR26955</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>2026857</t>
+          <t>20261076</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
@@ -52601,12 +52601,12 @@
       </c>
       <c r="D1416" t="inlineStr">
         <is>
-          <t>شركة اسرار العمار للتطوير العقاري</t>
+          <t>عبير عبدالعزيز عبدالله الصالح</t>
         </is>
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1416" t="inlineStr">
@@ -52623,32 +52623,32 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>BLS-LR26973</t>
+          <t>BLS-LR269556</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>2026865</t>
+          <t>20268422</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>عطيه علي عطيه الغامدي</t>
         </is>
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1417" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1417" t="inlineStr">
@@ -52660,32 +52660,32 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>BLS-LR26978</t>
+          <t>BLS-LR269564</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>2026863</t>
+          <t>20268485</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
         <is>
-          <t>مؤسسة اجمل القصور للتطوير العقاري</t>
+          <t>سلطان سرحان محمد مرشد</t>
         </is>
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1418" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1418" t="inlineStr">
@@ -52697,32 +52697,32 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>BLS-LR26981</t>
+          <t>BLS-LR269566</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>2026867</t>
+          <t>20268425</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr">
         <is>
-          <t>جابر عبدالله ناصر الدخيل</t>
+          <t>محمد خالد بن محيل المطيري</t>
         </is>
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1419" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1419" t="inlineStr">
@@ -52734,32 +52734,32 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>BLS-LR26993</t>
+          <t>BLS-LR269570</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>2026886</t>
+          <t>20268435</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
         <is>
-          <t>شركة اتمام البناء للتطوير العقاري شركة شخص واحد</t>
+          <t>شجاع نهار نهير العميري</t>
         </is>
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1420" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1420" t="inlineStr">
@@ -52771,22 +52771,22 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>BLS-LR26994</t>
+          <t>BLS-LR269577</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>2026885</t>
+          <t>20268439</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1421" t="inlineStr">
         <is>
-          <t>مؤسسة ركاز الطيب</t>
+          <t>سبيل جودالله بنيان المطيري</t>
         </is>
       </c>
       <c r="E1421" t="inlineStr">
@@ -52796,7 +52796,7 @@
       </c>
       <c r="F1421" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1421" t="inlineStr">
@@ -52808,27 +52808,27 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>BLS-LR26995</t>
+          <t>BLS-LR26958</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>2026888</t>
+          <t>2026836</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1422" t="inlineStr">
         <is>
-          <t>شركة حمد محمد بن سعيدان العقارية</t>
+          <t>ذعار عايض ذعار العجمي</t>
         </is>
       </c>
       <c r="E1422" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1422" t="inlineStr">
@@ -52845,32 +52845,32 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>BLS-LR26997</t>
+          <t>BLS-LR269597</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>2026891</t>
+          <t>20268462</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1423" t="inlineStr">
         <is>
-          <t>ناصر محمد ناصر آل مسلم</t>
+          <t>الجمعية الدعوية للصم</t>
         </is>
       </c>
       <c r="E1423" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1423" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1423" t="inlineStr">
@@ -52882,22 +52882,22 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>GBLS-LR261707</t>
+          <t>BLS-LR269602</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>20262186</t>
+          <t>20268466</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>١٧ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1424" t="inlineStr">
@@ -52907,259 +52907,263 @@
       </c>
       <c r="F1424" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1424" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>GBLS-LR261803</t>
+          <t>BLS-LR269608</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>20263361</t>
+          <t>20268469</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>٢٠ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>فيصل بن سلطان بن فيصل آل سعود</t>
         </is>
       </c>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1425" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1425" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>GBLS-LR262615</t>
+          <t>BLS-LR269617</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>20262341</t>
+          <t>20268476</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>٢١ - ذو الحجة - ١٤٤٧ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مؤسسة فناء الريحان للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1426" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1426" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>GBLS-LR263537</t>
+          <t>BLS-LR269630</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>20263323</t>
+          <t>20268486</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>٨ - محرم - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مناحي بن مطلق بن مطير الغامدي</t>
         </is>
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1427" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1427" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>GBLS-LR263578</t>
+          <t>BLS-LR269635</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>20263402</t>
+          <t>20268494</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مشعل شليل بن حبيب المطيري</t>
         </is>
       </c>
       <c r="E1428" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1428" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1428" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>GBLS-LR264227</t>
+          <t>BLS-LR269679</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>20263765</t>
+          <t>20268519</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>شركة واعد العقارية</t>
         </is>
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1429" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1429" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>GBLS-LR264447</t>
+          <t>BLS-LR26968</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>20264047</t>
+          <t>20261517</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>٢٢ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>حراز سعيد عايض العتيبي</t>
         </is>
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1430" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1430" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>GBLS-LR264953</t>
+          <t>BLS-LR26969</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>20264430</t>
+          <t>2026858</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
-        </is>
-      </c>
-      <c r="E1431" t="inlineStr"/>
+          <t>مؤسسة شوق حميد المطيري للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>حي ضاحية نمار</t>
+        </is>
+      </c>
       <c r="F1431" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -53167,66 +53171,66 @@
       </c>
       <c r="G1431" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>GBLS-LR265064</t>
+          <t>BLS-LR269692</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>20264519</t>
+          <t>20268517</t>
         </is>
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1432" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>عبدالرحمن عثمان محمد العياف</t>
         </is>
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1432" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1432" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>GBLS-LR266387</t>
+          <t>BLS-LR26971</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>20265632</t>
+          <t>20261495</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>١٩ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1433" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مؤسسة قدم العقارية</t>
         </is>
       </c>
       <c r="E1433" t="inlineStr">
@@ -53241,34 +53245,34 @@
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>GBLS-LR266569</t>
+          <t>BLS-LR26972</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>20265786</t>
+          <t>2026857</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>٢١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>شركة اسرار العمار للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1434" t="inlineStr">
@@ -53278,140 +53282,140 @@
       </c>
       <c r="G1434" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>GBLS-LR267898</t>
+          <t>BLS-LR269723</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>20267572</t>
+          <t>20268535</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>١١ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>شديد حمد مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1435" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>توزيع الطلب</t>
         </is>
       </c>
       <c r="G1435" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>GBLS-LR268067</t>
+          <t>BLS-LR26973</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>20268306</t>
+          <t>2026865</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1436" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1436" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>OST-LR264090</t>
+          <t>BLS-LR26978</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>20262152</t>
+          <t>2026863</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>١٧ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">
         <is>
-          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
+          <t>مؤسسة اجمل القصور للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1437" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1437" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>OST-LR264772</t>
+          <t>BLS-LR26981</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>20262152</t>
+          <t>2026867</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>٢٧ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
         <is>
-          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
+          <t>جابر عبدالله ناصر الدخيل</t>
         </is>
       </c>
       <c r="E1438" t="inlineStr">
@@ -53426,34 +53430,34 @@
       </c>
       <c r="G1438" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>OST-LR265023</t>
+          <t>BLS-LR26993</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>2026613</t>
+          <t>2026886</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1439" t="inlineStr">
         <is>
-          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
+          <t>شركة اتمام البناء للتطوير العقاري شركة شخص واحد</t>
         </is>
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1439" t="inlineStr">
@@ -53463,71 +53467,71 @@
       </c>
       <c r="G1439" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>OST-LR266524</t>
+          <t>BLS-LR26994</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>20262767</t>
+          <t>2026885</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1440" t="inlineStr">
         <is>
-          <t>خالد شاهر بن مصلح المطيري</t>
+          <t>مؤسسة ركاز الطيب</t>
         </is>
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1440" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1440" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>OST-LR268954</t>
+          <t>BLS-LR26995</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>20265645</t>
+          <t>2026888</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
         <is>
-          <t>مؤسسة عنوان الرفيعة للتطوير والاستثمار العقاري</t>
+          <t>شركة حمد محمد بن سعيدان العقارية</t>
         </is>
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1441" t="inlineStr">
@@ -53537,71 +53541,71 @@
       </c>
       <c r="G1441" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>OST-LR269061</t>
+          <t>BLS-LR26997</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>20265551</t>
+          <t>2026891</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1442" t="inlineStr">
         <is>
-          <t>ناصر ظافر بن جديع ال فهاد</t>
+          <t>ناصر محمد ناصر آل مسلم</t>
         </is>
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1442" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1442" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>RUS-LR261413</t>
+          <t>GBLS-LR261707</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>2026629</t>
+          <t>20262186</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>٦ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>١٧ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
         <is>
-          <t>عبدالعزيز ناصر سعد السعد</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1443" t="inlineStr">
@@ -53611,34 +53615,34 @@
       </c>
       <c r="G1443" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>RUS-LR263097</t>
+          <t>GBLS-LR261803</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>20262566</t>
+          <t>20263361</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>٢٩ - ذو الحجة - ١٤٤٧ هـ</t>
+          <t>٢٠ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">
         <is>
-          <t>عبدالرحمن ابراهيم عبدالعزيز العريني</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1444" t="inlineStr">
@@ -53648,71 +53652,71 @@
       </c>
       <c r="G1444" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>RUS-LR264967</t>
+          <t>GBLS-LR262615</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>20262341</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - ذو الحجة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1445" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>RUS-LR264969</t>
+          <t>GBLS-LR263537</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>20262723</t>
+          <t>20263323</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٨ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
         <is>
-          <t>معدى صنيتان رازن العتيبي</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1446" t="inlineStr">
@@ -53722,66 +53726,66 @@
       </c>
       <c r="G1446" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>RUS-LR264980</t>
+          <t>GBLS-LR263578</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>20261050</t>
+          <t>20263402</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1447" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>RUS-LR265038</t>
+          <t>GBLS-LR264227</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>2026378</t>
+          <t>20263765</t>
         </is>
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1448" t="inlineStr">
@@ -53796,34 +53800,34 @@
       </c>
       <c r="G1448" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>RUS-LR265039</t>
+          <t>GBLS-LR264447</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>2026817</t>
+          <t>20264047</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٢ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1449" t="inlineStr">
@@ -53833,56 +53837,52 @@
       </c>
       <c r="G1449" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>RUS-LR265040</t>
+          <t>GBLS-LR264953</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>2026379</t>
+          <t>20264430</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
-        </is>
-      </c>
-      <c r="E1450" t="inlineStr">
-        <is>
-          <t>حي طويق</t>
-        </is>
-      </c>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr"/>
       <c r="F1450" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1450" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>RUS-LR265045</t>
+          <t>GBLS-LR265064</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>20261977</t>
+          <t>20264519</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
@@ -53892,86 +53892,86 @@
       </c>
       <c r="D1451" t="inlineStr">
         <is>
-          <t>شركة ثرى الشراكة العقارية</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1451" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1451" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>RUS-LR265080</t>
+          <t>GBLS-LR266387</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>2026902</t>
+          <t>20265632</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>١٩ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
         <is>
-          <t>محمد عبدالله محمد الحقيل</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>حي الخزامى</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1452" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1452" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>RUS-LR265271</t>
+          <t>GBLS-LR266569</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>20261204</t>
+          <t>20265786</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>٢١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
         <is>
-          <t>سلطان سالم سلمان العميري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1453" t="inlineStr">
@@ -53981,71 +53981,71 @@
       </c>
       <c r="G1453" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>RUS-LR265311</t>
+          <t>GBLS-LR267898</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>20261011</t>
+          <t>20267572</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>١١ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
         <is>
-          <t>محمد مسفر سعد البقمي</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1454" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1454" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>RUS-LR265318</t>
+          <t>GBLS-LR268067</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>20261025</t>
+          <t>20268306</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
         <is>
-          <t>محمد مسفر سعد البقمي</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1455" t="inlineStr">
@@ -54055,66 +54055,66 @@
       </c>
       <c r="G1455" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>RUS-LR265377</t>
+          <t>OST-LR264090</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>20262926</t>
+          <t>20262152</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1456" t="inlineStr">
         <is>
-          <t>شركة تأصيل العقارية</t>
+          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
         </is>
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1456" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1456" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>RUS-LR265391</t>
+          <t>OST-LR264772</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>20263986</t>
+          <t>20262152</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
         <is>
-          <t>مؤسسة طالب مويس منيع المطيري للتطوير العقاري</t>
+          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
         </is>
       </c>
       <c r="E1457" t="inlineStr">
@@ -54129,34 +54129,34 @@
       </c>
       <c r="G1457" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>RUS-LR265422</t>
+          <t>OST-LR265023</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>20263002</t>
+          <t>2026613</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
         <is>
-          <t>محمد سعد محمد الوادعي</t>
+          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1458" t="inlineStr">
@@ -54166,34 +54166,34 @@
       </c>
       <c r="G1458" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>RUS-LR265483</t>
+          <t>OST-LR266524</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>20263669</t>
+          <t>20262767</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
         <is>
-          <t>عبدالعزيز محمد حسن العتيبي</t>
+          <t>خالد شاهر بن مصلح المطيري</t>
         </is>
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1459" t="inlineStr">
@@ -54203,29 +54203,29 @@
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>RUS-LR265493</t>
+          <t>OST-LR268954</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>20263649</t>
+          <t>20265645</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
         <is>
-          <t>وفاء عبدالله حمد المنيع</t>
+          <t>مؤسسة عنوان الرفيعة للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1460" t="inlineStr">
@@ -54240,76 +54240,76 @@
       </c>
       <c r="G1460" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>RUS-LR265568</t>
+          <t>OST-LR269061</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>20263528</t>
+          <t>20265551</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>ناصر ظافر بن جديع ال فهاد</t>
         </is>
       </c>
       <c r="E1461" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1461" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1461" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>RUS-LR265623</t>
+          <t>RUS-LR261413</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>2026629</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>عبدالعزيز ناصر سعد السعد</t>
         </is>
       </c>
       <c r="E1462" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1462" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1462" t="inlineStr">
@@ -54321,27 +54321,27 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>RUS-LR265625</t>
+          <t>RUS-LR263097</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>20261977</t>
+          <t>20262566</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - ذو الحجة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
         <is>
-          <t>شركة ثرى الشراكة العقارية</t>
+          <t>عبدالرحمن ابراهيم عبدالعزيز العريني</t>
         </is>
       </c>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1463" t="inlineStr">
@@ -54358,27 +54358,27 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>RUS-LR265709</t>
+          <t>RUS-LR264967</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>20261304</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
         <is>
-          <t>شركة فناء الإبتكار للتطوير العقاري</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>حي العوالي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1464" t="inlineStr">
@@ -54395,27 +54395,27 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>RUS-LR265869</t>
+          <t>RUS-LR264969</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>20261829</t>
+          <t>20262723</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr">
         <is>
-          <t>منى محمدمساعد خالد الحكيم</t>
+          <t>معدى صنيتان رازن العتيبي</t>
         </is>
       </c>
       <c r="E1465" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1465" t="inlineStr">
@@ -54432,27 +54432,27 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>RUS-LR265881</t>
+          <t>RUS-LR264980</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>20262926</t>
+          <t>20261050</t>
         </is>
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>شركة تأصيل العقارية</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1466" t="inlineStr">
@@ -54469,27 +54469,27 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>RUS-LR265941</t>
+          <t>RUS-LR265038</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>2026241</t>
+          <t>2026378</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
         <is>
-          <t>هلال حمدان غازي العتيبي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1467" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1467" t="inlineStr">
@@ -54506,22 +54506,22 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>RUS-LR265989</t>
+          <t>RUS-LR265039</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>20263868</t>
+          <t>2026817</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>١٣ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
         <is>
-          <t>نايف محمد صنهات السبيعي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1468" t="inlineStr">
@@ -54543,69 +54543,69 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>RUS-LR266100</t>
+          <t>RUS-LR265040</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>20264470</t>
+          <t>2026379</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>١٤ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
         <is>
-          <t>مؤسسة جدر العربية للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1469" t="inlineStr">
         <is>
-          <t>حي العريجاء الوسطى</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1469" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1469" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>RUS-LR266155</t>
+          <t>RUS-LR265045</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>2026379</t>
+          <t>20261977</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>شركة ثرى الشراكة العقارية</t>
         </is>
       </c>
       <c r="E1470" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1470" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1470" t="inlineStr">
@@ -54617,32 +54617,32 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>RUS-LR266384</t>
+          <t>RUS-LR265080</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>20264824</t>
+          <t>2026902</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>١٩ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
         <is>
-          <t>عبدالحكيم علي عبده محمد الحكمي</t>
+          <t>محمد عبدالله محمد الحقيل</t>
         </is>
       </c>
       <c r="E1471" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي الخزامى</t>
         </is>
       </c>
       <c r="F1471" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1471" t="inlineStr">
@@ -54654,27 +54654,27 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>RUS-LR266540</t>
+          <t>RUS-LR265271</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>20261645</t>
+          <t>20261204</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>٢١ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
         <is>
-          <t>مؤسسة مباني الورود للتطوير العقاري</t>
+          <t>سلطان سالم سلمان العميري</t>
         </is>
       </c>
       <c r="E1472" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1472" t="inlineStr">
@@ -54691,27 +54691,27 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>RUS-LR266691</t>
+          <t>RUS-LR265311</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>202517</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>٢٣ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
         <is>
-          <t>ماجد بن عبدالله نابت الشهراني</t>
+          <t>محمد مسفر سعد البقمي</t>
         </is>
       </c>
       <c r="E1473" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1473" t="inlineStr">
@@ -54728,32 +54728,32 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>RUS-LR266771</t>
+          <t>RUS-LR265318</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>20262626</t>
+          <t>20261025</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
         <is>
-          <t>بزيع سليمان بزيع المبارك</t>
+          <t>محمد مسفر سعد البقمي</t>
         </is>
       </c>
       <c r="E1474" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1474" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1474" t="inlineStr">
@@ -54765,22 +54765,22 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>RUS-LR266803</t>
+          <t>RUS-LR265377</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>20264988</t>
+          <t>20262926</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
         <is>
-          <t>سلطان بن منير بن منيف البقمي</t>
+          <t>شركة تأصيل العقارية</t>
         </is>
       </c>
       <c r="E1475" t="inlineStr">
@@ -54790,7 +54790,7 @@
       </c>
       <c r="F1475" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1475" t="inlineStr">
@@ -54802,27 +54802,27 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>RUS-LR266814</t>
+          <t>RUS-LR265391</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>2026605</t>
+          <t>20263986</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
         <is>
-          <t>مؤسسة فهد سعود اليوسف</t>
+          <t>مؤسسة طالب مويس منيع المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1476" t="inlineStr">
@@ -54839,22 +54839,22 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>RUS-LR266930</t>
+          <t>RUS-LR265422</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>20265106</t>
+          <t>20263002</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
         <is>
-          <t>عبدالهادي جعفر خنثل بن شري</t>
+          <t>محمد سعد محمد الوادعي</t>
         </is>
       </c>
       <c r="E1477" t="inlineStr">
@@ -54876,27 +54876,27 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>RUS-LR266984</t>
+          <t>RUS-LR265483</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>2026902</t>
+          <t>20263669</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1478" t="inlineStr">
         <is>
-          <t>محمد عبدالله محمد الحقيل</t>
+          <t>عبدالعزيز محمد حسن العتيبي</t>
         </is>
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>حي الخزامى</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1478" t="inlineStr">
@@ -54906,34 +54906,34 @@
       </c>
       <c r="G1478" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>RUS-LR266991</t>
+          <t>RUS-LR265493</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>20265006</t>
+          <t>20263649</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
         <is>
-          <t>شركة وتد الديار</t>
+          <t>وفاء عبدالله حمد المنيع</t>
         </is>
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1479" t="inlineStr">
@@ -54950,32 +54950,32 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>RUS-LR266993</t>
+          <t>RUS-LR265568</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>20265012</t>
+          <t>20263528</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
         <is>
-          <t>شركة وتد الديار</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1480" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1480" t="inlineStr">
@@ -54987,32 +54987,32 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>RUS-LR267452</t>
+          <t>RUS-LR265623</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>2026865</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1481" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1481" t="inlineStr">
@@ -55024,27 +55024,27 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>RUS-LR267541</t>
+          <t>RUS-LR265625</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>20263700</t>
+          <t>20261977</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr">
         <is>
-          <t>مؤسسة نرجس المبانى للتطوير العقاري</t>
+          <t>شركة ثرى الشراكة العقارية</t>
         </is>
       </c>
       <c r="E1482" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1482" t="inlineStr">
@@ -55061,32 +55061,32 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>RUS-LR267556</t>
+          <t>RUS-LR265709</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>20263440</t>
+          <t>20261304</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr">
         <is>
-          <t>ابراهيم فائز ابراهيم القحطاني</t>
+          <t>شركة فناء الإبتكار للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1483" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1483" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1483" t="inlineStr">
@@ -55098,27 +55098,27 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>RUS-LR267632</t>
+          <t>RUS-LR265869</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>2026613</t>
+          <t>20261829</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
         <is>
-          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
+          <t>منى محمدمساعد خالد الحكيم</t>
         </is>
       </c>
       <c r="E1484" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1484" t="inlineStr">
@@ -55135,28 +55135,32 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>RUS-LR267647</t>
+          <t>RUS-LR265881</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>20264482</t>
+          <t>20262926</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
         <is>
-          <t>عناد عاتق عيد العميرى</t>
-        </is>
-      </c>
-      <c r="E1485" t="inlineStr"/>
+          <t>شركة تأصيل العقارية</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>حي ضاحية نمار</t>
+        </is>
+      </c>
       <c r="F1485" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1485" t="inlineStr">
@@ -55168,27 +55172,27 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>RUS-LR267651</t>
+          <t>RUS-LR265941</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>20262551</t>
+          <t>2026241</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr">
         <is>
-          <t>عناد عاتق عيد العميرى</t>
+          <t>هلال حمدان غازي العتيبي</t>
         </is>
       </c>
       <c r="E1486" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1486" t="inlineStr">
@@ -55205,22 +55209,22 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>RUS-LR267722</t>
+          <t>RUS-LR265989</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>20264896</t>
+          <t>20263868</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٣ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
         <is>
-          <t>عبدالعزيز بن على بن سمران الحربي</t>
+          <t>نايف محمد صنهات السبيعي</t>
         </is>
       </c>
       <c r="E1487" t="inlineStr">
@@ -55242,25 +55246,29 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>RUS-LR267741</t>
+          <t>RUS-LR266100</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>20264382</t>
+          <t>20264470</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
         <is>
-          <t>عبدالرحمن سعود محمد الخريف</t>
-        </is>
-      </c>
-      <c r="E1488" t="inlineStr"/>
+          <t>مؤسسة جدر العربية للتطوير والاستثمار العقاري</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>حي العريجاء الوسطى</t>
+        </is>
+      </c>
       <c r="F1488" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -55268,34 +55276,34 @@
       </c>
       <c r="G1488" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>RUS-LR267767</t>
+          <t>RUS-LR266155</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>2026379</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1489" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1489" t="inlineStr">
@@ -55312,27 +55320,27 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>RUS-LR268079</t>
+          <t>RUS-LR266384</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>2026394</t>
+          <t>20264824</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٩ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>عبدالحكيم علي عبده محمد الحكمي</t>
         </is>
       </c>
       <c r="E1490" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1490" t="inlineStr">
@@ -55349,27 +55357,27 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>RUS-LR268340</t>
+          <t>RUS-LR266540</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>20264221</t>
+          <t>20261645</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>بدر محمد بن حثيري البقمي</t>
+          <t>مؤسسة مباني الورود للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1491" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1491" t="inlineStr">
@@ -55386,22 +55394,22 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>RUS-LR268470</t>
+          <t>RUS-LR266691</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>20261779</t>
+          <t>202517</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٣ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr">
         <is>
-          <t>مؤسسة التطوير النموذجية للتطوير العقاري</t>
+          <t>ماجد بن عبدالله نابت الشهراني</t>
         </is>
       </c>
       <c r="E1492" t="inlineStr">
@@ -55411,7 +55419,7 @@
       </c>
       <c r="F1492" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1492" t="inlineStr">
@@ -55423,22 +55431,22 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>RUS-LR268532</t>
+          <t>RUS-LR266771</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>2026394</t>
+          <t>20262626</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>بزيع سليمان بزيع المبارك</t>
         </is>
       </c>
       <c r="E1493" t="inlineStr">
@@ -55448,7 +55456,7 @@
       </c>
       <c r="F1493" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1493" t="inlineStr">
@@ -55460,59 +55468,59 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>RUS-LR268621</t>
+          <t>RUS-LR266803</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>20263528</t>
+          <t>20264988</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>سلطان بن منير بن منيف البقمي</t>
         </is>
       </c>
       <c r="E1494" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1494" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1494" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>RUS-LR268843</t>
+          <t>RUS-LR266814</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>20266365</t>
+          <t>2026605</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
         <is>
-          <t>خالد بن سعد بن سعود العصيمي</t>
+          <t>مؤسسة فهد سعود اليوسف</t>
         </is>
       </c>
       <c r="E1495" t="inlineStr">
@@ -55534,25 +55542,29 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>RUS-LR268863</t>
+          <t>RUS-LR266930</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>20264382</t>
+          <t>20265106</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
         <is>
-          <t>عبدالرحمن سعود محمد الخريف</t>
-        </is>
-      </c>
-      <c r="E1496" t="inlineStr"/>
+          <t>عبدالهادي جعفر خنثل بن شري</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>حي ضاحية نمار</t>
+        </is>
+      </c>
       <c r="F1496" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -55567,64 +55579,64 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>RUS-LR268896</t>
+          <t>RUS-LR266984</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>20261892</t>
+          <t>2026902</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
         <is>
-          <t>عبدالله ابن علي ابن شايع ال شفلوت</t>
+          <t>محمد عبدالله محمد الحقيل</t>
         </is>
       </c>
       <c r="E1497" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الخزامى</t>
         </is>
       </c>
       <c r="F1497" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1497" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>RUS-LR268922</t>
+          <t>RUS-LR266991</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>2026916</t>
+          <t>20265006</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
         <is>
-          <t>علي عائض بن علي البقمي</t>
+          <t>شركة وتد الديار</t>
         </is>
       </c>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1498" t="inlineStr">
@@ -55641,27 +55653,27 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>RUS-LR269043</t>
+          <t>RUS-LR266993</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>20266122</t>
+          <t>20265012</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr">
         <is>
-          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
+          <t>شركة وتد الديار</t>
         </is>
       </c>
       <c r="E1499" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1499" t="inlineStr">
@@ -55678,22 +55690,22 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>RUS-LR269055</t>
+          <t>RUS-LR267452</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>20263495</t>
+          <t>2026865</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1500" t="inlineStr">
@@ -55715,32 +55727,32 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>RUS-LR269087</t>
+          <t>RUS-LR267541</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>20266955</t>
+          <t>20263700</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr">
         <is>
-          <t>نواف عبدالله حسين القحطاني</t>
+          <t>مؤسسة نرجس المبانى للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1501" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1501" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1501" t="inlineStr">
@@ -55752,32 +55764,32 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>RUS-LR269169</t>
+          <t>RUS-LR267556</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>20266137</t>
+          <t>20263440</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr">
         <is>
-          <t>شركة رصين نجد العقارية</t>
+          <t>ابراهيم فائز ابراهيم القحطاني</t>
         </is>
       </c>
       <c r="E1502" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1502" t="inlineStr">
         <is>
-          <t>ملغي</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1502" t="inlineStr">
@@ -55789,32 +55801,32 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>RUS-LR269180</t>
+          <t>RUS-LR267632</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>20262394</t>
+          <t>2026613</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr">
         <is>
-          <t>محمد عبدالوهاب سلوم السلوم</t>
+          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1503" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1503" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1503" t="inlineStr">
@@ -55826,32 +55838,28 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>RUS-LR269184</t>
+          <t>RUS-LR267647</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>2026734</t>
+          <t>20264482</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr">
         <is>
-          <t>مؤسسة عبدالعزيز بن جلوي بن محارب المطيري</t>
-        </is>
-      </c>
-      <c r="E1504" t="inlineStr">
-        <is>
-          <t>حي العريجاء الغربي</t>
-        </is>
-      </c>
+          <t>عناد عاتق عيد العميرى</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr"/>
       <c r="F1504" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1504" t="inlineStr">
@@ -55863,27 +55871,27 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>RUS-LR269207</t>
+          <t>RUS-LR267651</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>20263023</t>
+          <t>20262551</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>عائض عبدالله مبارك القحطاني</t>
+          <t>عناد عاتق عيد العميرى</t>
         </is>
       </c>
       <c r="E1505" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1505" t="inlineStr">
@@ -55893,34 +55901,34 @@
       </c>
       <c r="G1505" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>RUS-LR269208</t>
+          <t>RUS-LR267722</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>20263021</t>
+          <t>20264896</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>عائض عبدالله مبارك القحطاني</t>
+          <t>عبدالعزيز بن على بن سمران الحربي</t>
         </is>
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1506" t="inlineStr">
@@ -55930,36 +55938,32 @@
       </c>
       <c r="G1506" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>RUS-LR269243</t>
+          <t>RUS-LR267741</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>20266137</t>
+          <t>20264382</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr">
         <is>
-          <t>شركة رصين نجد العقارية</t>
-        </is>
-      </c>
-      <c r="E1507" t="inlineStr">
-        <is>
-          <t>حي الحزم</t>
-        </is>
-      </c>
+          <t>عبدالرحمن سعود محمد الخريف</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr"/>
       <c r="F1507" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -55974,22 +55978,22 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>RUS-LR269411</t>
+          <t>RUS-LR267767</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>20267329</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1508" t="inlineStr">
         <is>
-          <t>مؤسسة مجد الوفاء للتطوير العقاري</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1508" t="inlineStr">
@@ -55999,7 +56003,7 @@
       </c>
       <c r="F1508" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1508" t="inlineStr">
@@ -56011,27 +56015,27 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>SIP-LR264068</t>
+          <t>RUS-LR268079</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>20263876</t>
+          <t>2026394</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>١٧ - محرم - ١٤٤٨ هـ</t>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr">
         <is>
-          <t>نوره عبدالعزيز محمد العريفي</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1509" t="inlineStr">
@@ -56041,34 +56045,34 @@
       </c>
       <c r="G1509" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>SIP-LR264320</t>
+          <t>RUS-LR268340</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>20264534</t>
+          <t>20264221</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
+          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr">
         <is>
-          <t>شركة مدماك الغد العقارية</t>
+          <t>بدر محمد بن حثيري البقمي</t>
         </is>
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1510" t="inlineStr">
@@ -56078,34 +56082,34 @@
       </c>
       <c r="G1510" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>SIP-LR264372</t>
+          <t>RUS-LR268470</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>20263907</t>
+          <t>20261779</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr">
         <is>
-          <t>٢١ - محرم - ١٤٤٨ هـ</t>
+          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
+          <t>مؤسسة التطوير النموذجية للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1511" t="inlineStr">
@@ -56115,34 +56119,34 @@
       </c>
       <c r="G1511" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>SIP-LR265231</t>
+          <t>RUS-LR268532</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>20264645</t>
+          <t>2026394</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>٢ - صفر - ١٤٤٨ هـ</t>
+          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>علي بن محمد بن مسفر الحلافي</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1512" t="inlineStr">
@@ -56152,71 +56156,71 @@
       </c>
       <c r="G1512" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>SIP-LR265499</t>
+          <t>RUS-LR268621</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>20264866</t>
+          <t>20263528</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>شركة المسكن الأمثل للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1513" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1513" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1513" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>SIP-LR265502</t>
+          <t>RUS-LR268843</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>20264858</t>
+          <t>20266365</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
-          <t>سلطان ناصر زيد بن شنار</t>
+          <t>خالد بن سعد بن سعود العصيمي</t>
         </is>
       </c>
       <c r="E1514" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1514" t="inlineStr">
@@ -56226,36 +56230,32 @@
       </c>
       <c r="G1514" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>SIP-LR265662</t>
+          <t>RUS-LR268863</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>20264983</t>
+          <t>20264382</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>عمر ابن عبدالعزيز ابن عبدالله الغامدي</t>
-        </is>
-      </c>
-      <c r="E1515" t="inlineStr">
-        <is>
-          <t>حي العريجاء الغربي</t>
-        </is>
-      </c>
+          <t>عبدالرحمن سعود محمد الخريف</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr"/>
       <c r="F1515" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56263,29 +56263,29 @@
       </c>
       <c r="G1515" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>SIP-LR265713</t>
+          <t>RUS-LR268896</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>20265038</t>
+          <t>20261892</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>فهده سفر بهيشان الحافي</t>
+          <t>عبدالله ابن علي ابن شايع ال شفلوت</t>
         </is>
       </c>
       <c r="E1516" t="inlineStr">
@@ -56295,39 +56295,39 @@
       </c>
       <c r="F1516" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1516" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>SIP-LR265893</t>
+          <t>RUS-LR268922</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>20265178</t>
+          <t>2026916</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>مؤسسة محمد علي محمد التميمي للتطوير العقاري</t>
+          <t>علي عائض بن علي البقمي</t>
         </is>
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1517" t="inlineStr">
@@ -56337,34 +56337,34 @@
       </c>
       <c r="G1517" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>SIP-LR266235</t>
+          <t>RUS-LR269043</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>20265492</t>
+          <t>20266122</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
         </is>
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1518" t="inlineStr">
@@ -56374,29 +56374,29 @@
       </c>
       <c r="G1518" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>SIP-LR266237</t>
+          <t>RUS-LR269055</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>20265494</t>
+          <t>20263495</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1519" t="inlineStr">
@@ -56411,108 +56411,108 @@
       </c>
       <c r="G1519" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>SIP-LR266243</t>
+          <t>RUS-LR269087</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>20265495</t>
+          <t>20266955</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>نواف عبدالله حسين القحطاني</t>
         </is>
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1520" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1520" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>SIP-LR266356</t>
+          <t>RUS-LR269169</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>20265660</t>
+          <t>20266137</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>١٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>شركة امثل للاستثمار</t>
+          <t>شركة رصين نجد العقارية</t>
         </is>
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1521" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1521" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>SIP-LR266526</t>
+          <t>RUS-LR269180</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>20265751</t>
+          <t>20262394</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+          <t>محمد عبدالوهاب سلوم السلوم</t>
         </is>
       </c>
       <c r="E1522" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1522" t="inlineStr">
@@ -56522,71 +56522,71 @@
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>SIP-LR266527</t>
+          <t>RUS-LR269184</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>20265752</t>
+          <t>2026734</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة عبدالعزيز بن جلوي بن محارب المطيري</t>
         </is>
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>SIP-LR266637</t>
+          <t>RUS-LR269207</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>20265853</t>
+          <t>20263023</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>حنان عبدالرحيم مطلق الاحمدي</t>
+          <t>عائض عبدالله مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1524" t="inlineStr">
@@ -56596,34 +56596,34 @@
       </c>
       <c r="G1524" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>SIP-LR266649</t>
+          <t>RUS-LR269208</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>20265864</t>
+          <t>20263021</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>مؤسسة الوجهة الحديثة للتطوير العقاري</t>
+          <t>عائض عبدالله مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1525" t="inlineStr">
@@ -56633,34 +56633,34 @@
       </c>
       <c r="G1525" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>SIP-LR266788</t>
+          <t>RUS-LR269243</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>20265977</t>
+          <t>20266137</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>عبدالعزيز مقعد مرزوق المطيري</t>
+          <t>شركة رصين نجد العقارية</t>
         </is>
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1526" t="inlineStr">
@@ -56670,34 +56670,34 @@
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>SIP-LR266976</t>
+          <t>RUS-LR269411</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>20266673</t>
+          <t>20267329</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>عبيد محمد مطلق العصيمي</t>
+          <t>مؤسسة مجد الوفاء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1527" t="inlineStr">
@@ -56707,108 +56707,108 @@
       </c>
       <c r="G1527" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>SIP-LR266985</t>
+          <t>RUS-LR269523</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>20266172</t>
+          <t>20263699</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1528" t="inlineStr">
         <is>
-          <t>شركة ساف العقارية</t>
+          <t>مسعود حسن بن قبحان الغامدي</t>
         </is>
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1528" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1528" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>SIP-LR267002</t>
+          <t>RUS-LR269592</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>20266182</t>
+          <t>20262178</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>٢٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>شركة ساف العقارية</t>
+          <t>شركة إثراء الرياض العقارية</t>
         </is>
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1529" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1529" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>SIP-LR267466</t>
+          <t>RUS-LR269603</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>20266601</t>
+          <t>20264202</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>شركة عمرانيات الجزيره للمقاولات</t>
+          <t>جابر علي احمد مجرشي</t>
         </is>
       </c>
       <c r="E1530" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1530" t="inlineStr">
@@ -56818,66 +56818,66 @@
       </c>
       <c r="G1530" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>SIP-LR267636</t>
+          <t>RUS-LR269641</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>20266785</t>
+          <t>20263967</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>شركة المسمات للتطوير والاستثمار العقاري شخص واحد</t>
+          <t>عبدالكريم دخيل الله خاتم السلمي</t>
         </is>
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1531" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1531" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>SIP-LR267770</t>
+          <t>RUS-LR269644</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>20266879</t>
+          <t>20261830</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>مؤسسة ارض وسكن للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1532" t="inlineStr">
@@ -56887,39 +56887,39 @@
       </c>
       <c r="F1532" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1532" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>SIP-LR267774</t>
+          <t>SIP-LR264068</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>20266887</t>
+          <t>20263876</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>نوره عبدالعزيز محمد العريفي</t>
         </is>
       </c>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1533" t="inlineStr">
@@ -56936,27 +56936,27 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>SIP-LR267777</t>
+          <t>SIP-LR264320</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>20266896</t>
+          <t>20264534</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>شركة مدماك الغد العقارية</t>
         </is>
       </c>
       <c r="E1534" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1534" t="inlineStr">
@@ -56973,27 +56973,27 @@
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>SIP-LR267816</t>
+          <t>SIP-LR264372</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>20266926</t>
+          <t>20263907</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢١ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>عبدالعزيز غيث موسى الغيث</t>
+          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
         </is>
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1535" t="inlineStr">
@@ -57010,27 +57010,27 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>SIP-LR267818</t>
+          <t>SIP-LR265231</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>20266927</t>
+          <t>20264645</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+          <t>علي بن محمد بن مسفر الحلافي</t>
         </is>
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1536" t="inlineStr">
@@ -57047,27 +57047,27 @@
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>SIP-LR268065</t>
+          <t>SIP-LR265499</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>20267343</t>
+          <t>20264866</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>عبدالعزيز صالح مبارك الماجد</t>
+          <t>شركة المسكن الأمثل للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1537" t="inlineStr">
@@ -57084,27 +57084,27 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>SIP-LR268337</t>
+          <t>SIP-LR265502</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>20267375</t>
+          <t>20264858</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>شركة الأماني العقارية (شركة شخص واحد)</t>
+          <t>سلطان ناصر زيد بن شنار</t>
         </is>
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
@@ -57121,27 +57121,27 @@
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>SIP-LR268611</t>
+          <t>SIP-LR265662</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>20267740</t>
+          <t>20264983</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>مؤسسة أوكن للتطوير العقاري</t>
+          <t>عمر ابن عبدالعزيز ابن عبدالله الغامدي</t>
         </is>
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1539" t="inlineStr">
@@ -57158,35 +57158,997 @@
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
+          <t>SIP-LR265713</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>20265038</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>فهده سفر بهيشان الحافي</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>حي ضاحية نمار</t>
+        </is>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>SIP-LR265893</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>20265178</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>مؤسسة محمد علي محمد التميمي للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>SIP-LR266235</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>20265492</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>SIP-LR266237</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>20265494</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>SIP-LR266243</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>20265495</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1544" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>SIP-LR266356</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>20265660</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>١٨ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>شركة امثل للاستثمار</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>حي ظهره لبن</t>
+        </is>
+      </c>
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>SIP-LR266526</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>20265751</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>SIP-LR266527</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>20265752</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>SIP-LR266637</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>20265853</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>حنان عبدالرحيم مطلق الاحمدي</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>حي عرقه</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>SIP-LR266649</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>20265864</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>مؤسسة الوجهة الحديثة للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>SIP-LR266788</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>20265977</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>عبدالعزيز مقعد مرزوق المطيري</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>SIP-LR266976</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>20266673</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>عبيد محمد مطلق العصيمي</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>حي طويق</t>
+        </is>
+      </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>SIP-LR266985</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>20266172</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>شركة ساف العقارية</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>حي نمار</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>SIP-LR267002</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>20266182</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>٢٨ - صفر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>شركة ساف العقارية</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>حي نمار</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>SIP-LR267466</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>20266601</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>شركة عمرانيات الجزيره للمقاولات</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>SIP-LR267636</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>20266785</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>شركة المسمات للتطوير والاستثمار العقاري شخص واحد</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>حي لبن</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>SIP-LR267770</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>20266879</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>شركة حلول التطوير العقارية</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>SIP-LR267774</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>20266887</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>شركة حلول التطوير العقارية</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>SIP-LR267777</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>20266896</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>شركة حلول التطوير العقارية</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>SIP-LR267816</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>20266926</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>عبدالعزيز غيث موسى الغيث</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>حي طويق</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>SIP-LR267818</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>20266927</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>SIP-LR268065</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>20267343</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>عبدالعزيز صالح مبارك الماجد</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>SIP-LR268337</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>20267375</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>شركة الأماني العقارية (شركة شخص واحد)</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>حي السويدي الغربي</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>SIP-LR268611</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>20267740</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>مؤسسة أوكن للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>حي ظهره لبن</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
           <t>SIP-LR269370</t>
         </is>
       </c>
-      <c r="B1540" t="inlineStr">
+      <c r="B1564" t="inlineStr">
         <is>
           <t>20268256</t>
         </is>
       </c>
-      <c r="C1540" t="inlineStr">
+      <c r="C1564" t="inlineStr">
         <is>
           <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
-      <c r="D1540" t="inlineStr">
+      <c r="D1564" t="inlineStr">
         <is>
           <t>محمد حمد عثمان الحسين</t>
         </is>
       </c>
-      <c r="E1540" t="inlineStr">
+      <c r="E1564" t="inlineStr">
         <is>
           <t>حي عرقه</t>
         </is>
       </c>
-      <c r="F1540" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="G1540" t="inlineStr">
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>SIP-LR269536</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>20268409</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>SIP-LR269720</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>20268540</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>مؤسسة عوالي الابداع للمقاولات</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>حي العوالي</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1566" t="inlineStr">
         <is>
           <t>تجهيز موقع</t>
         </is>

--- a/ups_requests.xlsx
+++ b/ups_requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1576"/>
+  <dimension ref="A1:G1581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -39673,7 +39673,7 @@
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1066" t="inlineStr">
@@ -41190,7 +41190,7 @@
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1107" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1175" t="inlineStr">
@@ -44257,7 +44257,7 @@
       </c>
       <c r="F1190" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1190" t="inlineStr">
@@ -45404,7 +45404,7 @@
       </c>
       <c r="F1221" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1221" t="inlineStr">
@@ -48105,7 +48105,7 @@
       </c>
       <c r="F1294" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1294" t="inlineStr">
@@ -49326,7 +49326,7 @@
       </c>
       <c r="F1327" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1327" t="inlineStr">
@@ -49400,7 +49400,7 @@
       </c>
       <c r="F1329" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1329" t="inlineStr">
@@ -49437,7 +49437,7 @@
       </c>
       <c r="F1330" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1330" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="F1349" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1349" t="inlineStr">
@@ -50510,7 +50510,7 @@
       </c>
       <c r="F1359" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1359" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1392" t="inlineStr">
@@ -51908,7 +51908,7 @@
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
@@ -52031,12 +52031,12 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>BLS-LR269415</t>
+          <t>BLS-LR269407</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>20268292</t>
+          <t>20268601</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
@@ -52046,17 +52046,17 @@
       </c>
       <c r="D1401" t="inlineStr">
         <is>
-          <t>محمد عبيد علي القحطاني</t>
+          <t>عبدالله محمد علي بن عون</t>
         </is>
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1401" t="inlineStr">
@@ -52068,12 +52068,12 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>BLS-LR269418</t>
+          <t>BLS-LR269415</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>20268471</t>
+          <t>20268292</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr">
@@ -52083,12 +52083,12 @@
       </c>
       <c r="D1402" t="inlineStr">
         <is>
-          <t>عبدالله محمد احمد القرني</t>
+          <t>محمد عبيد علي القحطاني</t>
         </is>
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1402" t="inlineStr">
@@ -52105,22 +52105,22 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>BLS-LR26943</t>
+          <t>BLS-LR269418</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>2026829</t>
+          <t>20268471</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr">
         <is>
-          <t>علي سعيد بن صنيتان المطيري</t>
+          <t>عبدالله محمد احمد القرني</t>
         </is>
       </c>
       <c r="E1403" t="inlineStr">
@@ -52130,7 +52130,7 @@
       </c>
       <c r="F1403" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1403" t="inlineStr">
@@ -52142,32 +52142,32 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>BLS-LR269444</t>
+          <t>BLS-LR26943</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>20268324</t>
+          <t>2026829</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1404" t="inlineStr">
         <is>
-          <t>مؤسسة مشارف المنزل للتجارة</t>
+          <t>علي سعيد بن صنيتان المطيري</t>
         </is>
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1404" t="inlineStr">
@@ -52179,12 +52179,12 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>BLS-LR269447</t>
+          <t>BLS-LR269444</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>20268316</t>
+          <t>20268324</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr">
@@ -52194,17 +52194,17 @@
       </c>
       <c r="D1405" t="inlineStr">
         <is>
-          <t>شركة مدينة الضباب للتطوير العقاري</t>
+          <t>مؤسسة مشارف المنزل للتجارة</t>
         </is>
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1405" t="inlineStr">
@@ -52216,27 +52216,27 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>BLS-LR26945</t>
+          <t>BLS-LR269447</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>2026950</t>
+          <t>20268316</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr">
         <is>
-          <t>ناصر عبدالله حجيلان الشيباني</t>
+          <t>شركة مدينة الضباب للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1406" t="inlineStr">
@@ -52253,32 +52253,32 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>BLS-LR269453</t>
+          <t>BLS-LR26945</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>20268319</t>
+          <t>2026950</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
         <is>
-          <t>علي محمد علي الأسمري</t>
+          <t>ناصر عبدالله حجيلان الشيباني</t>
         </is>
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1407" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1407" t="inlineStr">
@@ -52290,22 +52290,22 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>BLS-LR26946</t>
+          <t>BLS-LR269453</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>2026824</t>
+          <t>20268319</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1408" t="inlineStr">
         <is>
-          <t>سلطان مبارك بن مفلح القحطاني</t>
+          <t>علي محمد علي الأسمري</t>
         </is>
       </c>
       <c r="E1408" t="inlineStr">
@@ -52315,7 +52315,7 @@
       </c>
       <c r="F1408" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1408" t="inlineStr">
@@ -52327,27 +52327,27 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>BLS-LR269476</t>
+          <t>BLS-LR26946</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>20268371</t>
+          <t>2026824</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
         <is>
-          <t>وائل فائز رفدان الدوسري</t>
+          <t>سلطان مبارك بن مفلح القحطاني</t>
         </is>
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1409" t="inlineStr">
@@ -52364,27 +52364,27 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>BLS-LR26949</t>
+          <t>BLS-LR269476</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>2026827</t>
+          <t>20268371</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr">
         <is>
-          <t>سلطان مبارك بن مفلح القحطاني</t>
+          <t>وائل فائز رفدان الدوسري</t>
         </is>
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1410" t="inlineStr">
@@ -52401,22 +52401,22 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>BLS-LR269495</t>
+          <t>BLS-LR26949</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>20268370</t>
+          <t>2026827</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr">
         <is>
-          <t>مؤسسة وهج الجوهرة للتطوير والاستثمار العقاري</t>
+          <t>سلطان مبارك بن مفلح القحطاني</t>
         </is>
       </c>
       <c r="E1411" t="inlineStr">
@@ -52438,32 +52438,32 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>BLS-LR26950</t>
+          <t>BLS-LR269495</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>2026830</t>
+          <t>20268370</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة وهج الجوهرة للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1412" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1412" t="inlineStr">
@@ -52475,22 +52475,22 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>BLS-LR269500</t>
+          <t>BLS-LR26950</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>20268413</t>
+          <t>2026830</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr">
         <is>
-          <t>مسفر صالح عبدالله الدوسري</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1413" t="inlineStr">
@@ -52500,7 +52500,7 @@
       </c>
       <c r="F1413" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1413" t="inlineStr">
@@ -52512,12 +52512,12 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>BLS-LR269507</t>
+          <t>BLS-LR269500</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>20268367</t>
+          <t>20268413</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
@@ -52527,12 +52527,12 @@
       </c>
       <c r="D1414" t="inlineStr">
         <is>
-          <t>رشيد عبدالله سعيد السملق</t>
+          <t>مسفر صالح عبدالله الدوسري</t>
         </is>
       </c>
       <c r="E1414" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1414" t="inlineStr">
@@ -52549,32 +52549,32 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>BLS-LR26951</t>
+          <t>BLS-LR269507</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>2026832</t>
+          <t>20268367</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr">
         <is>
-          <t>ذعار عايض ذعار العجمي</t>
+          <t>رشيد عبدالله سعيد السملق</t>
         </is>
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1415" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1415" t="inlineStr">
@@ -52586,32 +52586,32 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>BLS-LR269525</t>
+          <t>BLS-LR26951</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>20268585</t>
+          <t>2026832</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr">
         <is>
-          <t>مؤسسة زبر للتطوير العقاري</t>
+          <t>ذعار عايض ذعار العجمي</t>
         </is>
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1416" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1416" t="inlineStr">
@@ -52623,12 +52623,12 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>BLS-LR269544</t>
+          <t>BLS-LR269525</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>20268414</t>
+          <t>20268585</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
@@ -52638,17 +52638,17 @@
       </c>
       <c r="D1417" t="inlineStr">
         <is>
-          <t>مؤسسة مبارك عبدالله بن مبارك آل مغيره للتطوير العقاري</t>
+          <t>مؤسسة زبر للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1417" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1417" t="inlineStr">
@@ -52660,12 +52660,12 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>BLS-LR269547</t>
+          <t>BLS-LR269544</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>20268421</t>
+          <t>20268414</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
@@ -52675,12 +52675,12 @@
       </c>
       <c r="D1418" t="inlineStr">
         <is>
-          <t>شركة استدامة الأعمال المالية</t>
+          <t>مؤسسة مبارك عبدالله بن مبارك آل مغيره للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>حي ظهره البديعه</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1418" t="inlineStr">
@@ -52697,32 +52697,32 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>BLS-LR26955</t>
+          <t>BLS-LR269547</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>20261076</t>
+          <t>20268421</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr">
         <is>
-          <t>عبير عبدالعزيز عبدالله الصالح</t>
+          <t>شركة استدامة الأعمال المالية</t>
         </is>
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ظهره البديعه</t>
         </is>
       </c>
       <c r="F1419" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1419" t="inlineStr">
@@ -52734,27 +52734,27 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>BLS-LR269556</t>
+          <t>BLS-LR26955</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>20268422</t>
+          <t>20261076</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
         <is>
-          <t>عطيه علي عطيه الغامدي</t>
+          <t>عبير عبدالعزيز عبدالله الصالح</t>
         </is>
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1420" t="inlineStr">
@@ -52771,12 +52771,12 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>BLS-LR269564</t>
+          <t>BLS-LR269556</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>20268485</t>
+          <t>20268422</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
@@ -52786,17 +52786,17 @@
       </c>
       <c r="D1421" t="inlineStr">
         <is>
-          <t>سلطان سرحان محمد مرشد</t>
+          <t>عطيه علي عطيه الغامدي</t>
         </is>
       </c>
       <c r="E1421" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1421" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1421" t="inlineStr">
@@ -52808,12 +52808,12 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>BLS-LR269566</t>
+          <t>BLS-LR269564</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>20268425</t>
+          <t>20268485</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr">
@@ -52823,17 +52823,17 @@
       </c>
       <c r="D1422" t="inlineStr">
         <is>
-          <t>محمد خالد بن محيل المطيري</t>
+          <t>سلطان سرحان محمد مرشد</t>
         </is>
       </c>
       <c r="E1422" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1422" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1422" t="inlineStr">
@@ -52845,12 +52845,12 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>BLS-LR269570</t>
+          <t>BLS-LR269566</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>20268435</t>
+          <t>20268425</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr">
@@ -52860,12 +52860,12 @@
       </c>
       <c r="D1423" t="inlineStr">
         <is>
-          <t>شجاع نهار نهير العميري</t>
+          <t>محمد خالد بن محيل المطيري</t>
         </is>
       </c>
       <c r="E1423" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1423" t="inlineStr">
@@ -52882,12 +52882,12 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>BLS-LR269577</t>
+          <t>BLS-LR269570</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>20268439</t>
+          <t>20268435</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr">
@@ -52897,17 +52897,17 @@
       </c>
       <c r="D1424" t="inlineStr">
         <is>
-          <t>سبيل جودالله بنيان المطيري</t>
+          <t>شجاع نهار نهير العميري</t>
         </is>
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1424" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1424" t="inlineStr">
@@ -52919,32 +52919,32 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>BLS-LR26958</t>
+          <t>BLS-LR269577</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>2026836</t>
+          <t>20268439</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
         <is>
-          <t>ذعار عايض ذعار العجمي</t>
+          <t>سبيل جودالله بنيان المطيري</t>
         </is>
       </c>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1425" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1425" t="inlineStr">
@@ -52956,32 +52956,32 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>BLS-LR269597</t>
+          <t>BLS-LR26958</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>20268462</t>
+          <t>2026836</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
         <is>
-          <t>الجمعية الدعوية للصم</t>
+          <t>ذعار عايض ذعار العجمي</t>
         </is>
       </c>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1426" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1426" t="inlineStr">
@@ -52993,12 +52993,12 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>BLS-LR269602</t>
+          <t>BLS-LR269597</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>20268466</t>
+          <t>20268462</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr">
@@ -53008,7 +53008,7 @@
       </c>
       <c r="D1427" t="inlineStr">
         <is>
-          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+          <t>الجمعية الدعوية للصم</t>
         </is>
       </c>
       <c r="E1427" t="inlineStr">
@@ -53030,12 +53030,12 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>BLS-LR269608</t>
+          <t>BLS-LR269602</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>20268469</t>
+          <t>20268466</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr">
@@ -53045,7 +53045,7 @@
       </c>
       <c r="D1428" t="inlineStr">
         <is>
-          <t>فيصل بن سلطان بن فيصل آل سعود</t>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1428" t="inlineStr">
@@ -53067,12 +53067,12 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>BLS-LR269617</t>
+          <t>BLS-LR269608</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>20268476</t>
+          <t>20268469</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
@@ -53082,12 +53082,12 @@
       </c>
       <c r="D1429" t="inlineStr">
         <is>
-          <t>مؤسسة فناء الريحان للتطوير العقاري</t>
+          <t>فيصل بن سلطان بن فيصل آل سعود</t>
         </is>
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1429" t="inlineStr">
@@ -53104,12 +53104,12 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>BLS-LR269630</t>
+          <t>BLS-LR269617</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>20268486</t>
+          <t>20268476</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr">
@@ -53119,17 +53119,17 @@
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>مناحي بن مطلق بن مطير الغامدي</t>
+          <t>مؤسسة فناء الريحان للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1430" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1430" t="inlineStr">
@@ -53141,12 +53141,12 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>BLS-LR269635</t>
+          <t>BLS-LR269630</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>20268494</t>
+          <t>20268486</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr">
@@ -53156,7 +53156,7 @@
       </c>
       <c r="D1431" t="inlineStr">
         <is>
-          <t>مشعل شليل بن حبيب المطيري</t>
+          <t>مناحي بن مطلق بن مطير الغامدي</t>
         </is>
       </c>
       <c r="E1431" t="inlineStr">
@@ -53166,7 +53166,7 @@
       </c>
       <c r="F1431" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1431" t="inlineStr">
@@ -53178,32 +53178,32 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>BLS-LR269679</t>
+          <t>BLS-LR269635</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>20268519</t>
+          <t>20268494</t>
         </is>
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1432" t="inlineStr">
         <is>
-          <t>شركة واعد العقارية</t>
+          <t>مشعل شليل بن حبيب المطيري</t>
         </is>
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1432" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1432" t="inlineStr">
@@ -53215,32 +53215,32 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>BLS-LR26968</t>
+          <t>BLS-LR269679</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>20261517</t>
+          <t>20268519</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1433" t="inlineStr">
         <is>
-          <t>حراز سعيد عايض العتيبي</t>
+          <t>شركة واعد العقارية</t>
         </is>
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1433" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1433" t="inlineStr">
@@ -53252,12 +53252,12 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>BLS-LR26969</t>
+          <t>BLS-LR26968</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>2026858</t>
+          <t>20261517</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr">
@@ -53267,7 +53267,7 @@
       </c>
       <c r="D1434" t="inlineStr">
         <is>
-          <t>مؤسسة شوق حميد المطيري للتطوير العقاري</t>
+          <t>حراز سعيد عايض العتيبي</t>
         </is>
       </c>
       <c r="E1434" t="inlineStr">
@@ -53277,7 +53277,7 @@
       </c>
       <c r="F1434" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1434" t="inlineStr">
@@ -53289,32 +53289,32 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>BLS-LR269692</t>
+          <t>BLS-LR26969</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>20268517</t>
+          <t>2026858</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>عبدالرحمن عثمان محمد العياف</t>
+          <t>مؤسسة شوق حميد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>حي العوالي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1435" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1435" t="inlineStr">
@@ -53326,32 +53326,32 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>BLS-LR26971</t>
+          <t>BLS-LR269692</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>20261495</t>
+          <t>20268517</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
         <is>
-          <t>مؤسسة قدم العقارية</t>
+          <t>عبدالرحمن عثمان محمد العياف</t>
         </is>
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1436" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1436" t="inlineStr">
@@ -53363,12 +53363,12 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>BLS-LR26972</t>
+          <t>BLS-LR26971</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>2026857</t>
+          <t>20261495</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
@@ -53378,12 +53378,12 @@
       </c>
       <c r="D1437" t="inlineStr">
         <is>
-          <t>شركة اسرار العمار للتطوير العقاري</t>
+          <t>مؤسسة قدم العقارية</t>
         </is>
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1437" t="inlineStr">
@@ -53400,32 +53400,32 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>BLS-LR269723</t>
+          <t>BLS-LR26972</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>20268535</t>
+          <t>2026857</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
         <is>
-          <t>شديد حمد مبارك القحطاني</t>
+          <t>شركة اسرار العمار للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1438" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1438" t="inlineStr">
@@ -53437,32 +53437,32 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>BLS-LR26973</t>
+          <t>BLS-LR269723</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>2026865</t>
+          <t>20268535</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1439" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>شديد حمد مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1439" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1439" t="inlineStr">
@@ -53474,32 +53474,32 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>BLS-LR269758</t>
+          <t>BLS-LR26973</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>20268557</t>
+          <t>2026865</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1440" t="inlineStr">
         <is>
-          <t>مؤسسة عبدالرحمن على عبدالعزيز المغامس للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1440" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1440" t="inlineStr">
@@ -53511,12 +53511,12 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>BLS-LR269773</t>
+          <t>BLS-LR269747</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>20268581</t>
+          <t>20268597</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
@@ -53526,17 +53526,17 @@
       </c>
       <c r="D1441" t="inlineStr">
         <is>
-          <t>بدريه فلاح عبدالعزيز العريفي</t>
+          <t>فالح ذعار فنيس القحطاني</t>
         </is>
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي العريجاء</t>
         </is>
       </c>
       <c r="F1441" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1441" t="inlineStr">
@@ -53548,12 +53548,12 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>BLS-LR269774</t>
+          <t>BLS-LR269758</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>20268568</t>
+          <t>20268557</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr">
@@ -53563,17 +53563,17 @@
       </c>
       <c r="D1442" t="inlineStr">
         <is>
-          <t>غانم حمود غانم العتيبي</t>
+          <t>مؤسسة عبدالرحمن على عبدالعزيز المغامس للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1442" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1442" t="inlineStr">
@@ -53585,12 +53585,12 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>BLS-LR269776</t>
+          <t>BLS-LR269773</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>20268570</t>
+          <t>20268581</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr">
@@ -53600,17 +53600,17 @@
       </c>
       <c r="D1443" t="inlineStr">
         <is>
-          <t>ناصر علي ناصر القحطاني</t>
+          <t>بدريه فلاح عبدالعزيز العريفي</t>
         </is>
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1443" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1443" t="inlineStr">
@@ -53622,32 +53622,32 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>BLS-LR26978</t>
+          <t>BLS-LR269774</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>2026863</t>
+          <t>20268568</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">
         <is>
-          <t>مؤسسة اجمل القصور للتطوير العقاري</t>
+          <t>غانم حمود غانم العتيبي</t>
         </is>
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1444" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1444" t="inlineStr">
@@ -53659,12 +53659,12 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>BLS-LR269783</t>
+          <t>BLS-LR269776</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>20268574</t>
+          <t>20268570</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr">
@@ -53684,7 +53684,7 @@
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1445" t="inlineStr">
@@ -53696,32 +53696,32 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>BLS-LR269791</t>
+          <t>BLS-LR26978</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>20268583</t>
+          <t>2026863</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
         <is>
-          <t>حسن معيض حسن الشهري</t>
+          <t>مؤسسة اجمل القصور للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1446" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1446" t="inlineStr">
@@ -53733,12 +53733,12 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>BLS-LR269798</t>
+          <t>BLS-LR269783</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>20268589</t>
+          <t>20268574</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr">
@@ -53748,17 +53748,17 @@
       </c>
       <c r="D1447" t="inlineStr">
         <is>
-          <t>عبدالرحمن خلوفه عوضه الشهري</t>
+          <t>ناصر علي ناصر القحطاني</t>
         </is>
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1447" t="inlineStr">
         <is>
-          <t>توزيع الطلب</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1447" t="inlineStr">
@@ -53770,32 +53770,32 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>BLS-LR26981</t>
+          <t>BLS-LR269791</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>2026867</t>
+          <t>20268583</t>
         </is>
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
         <is>
-          <t>جابر عبدالله ناصر الدخيل</t>
+          <t>حسن معيض حسن الشهري</t>
         </is>
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1448" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1448" t="inlineStr">
@@ -53807,32 +53807,32 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>BLS-LR26993</t>
+          <t>BLS-LR269796</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>2026886</t>
+          <t>20268595</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
         <is>
-          <t>شركة اتمام البناء للتطوير العقاري شركة شخص واحد</t>
+          <t>فهده فيحان دويريج العتيبي</t>
         </is>
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1449" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1449" t="inlineStr">
@@ -53844,32 +53844,32 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>BLS-LR26994</t>
+          <t>BLS-LR269798</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>2026885</t>
+          <t>20268589</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
         <is>
-          <t>مؤسسة ركاز الطيب</t>
+          <t>عبدالرحمن خلوفه عوضه الشهري</t>
         </is>
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1450" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1450" t="inlineStr">
@@ -53881,32 +53881,32 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>BLS-LR26995</t>
+          <t>BLS-LR269807</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>2026888</t>
+          <t>20268599</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
         <is>
-          <t>شركة حمد محمد بن سعيدان العقارية</t>
+          <t>شركة مدماك الغد العقارية</t>
         </is>
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1451" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1451" t="inlineStr">
@@ -53918,32 +53918,32 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>BLS-LR26997</t>
+          <t>BLS-LR26981</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>2026891</t>
+          <t>2026867</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
         <is>
-          <t>ناصر محمد ناصر آل مسلم</t>
+          <t>جابر عبدالله ناصر الدخيل</t>
         </is>
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1452" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1452" t="inlineStr">
@@ -53955,22 +53955,22 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>GBLS-LR261707</t>
+          <t>BLS-LR26993</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>20262186</t>
+          <t>2026886</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>١٧ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>شركة اتمام البناء للتطوير العقاري شركة شخص واحد</t>
         </is>
       </c>
       <c r="E1453" t="inlineStr">
@@ -53985,71 +53985,71 @@
       </c>
       <c r="G1453" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>GBLS-LR261803</t>
+          <t>BLS-LR26994</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>20263361</t>
+          <t>2026885</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>٢٠ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مؤسسة ركاز الطيب</t>
         </is>
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1454" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1454" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>GBLS-LR262615</t>
+          <t>BLS-LR26995</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>20262341</t>
+          <t>2026888</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>٢١ - ذو الحجة - ١٤٤٧ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>شركة حمد محمد بن سعيدان العقارية</t>
         </is>
       </c>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1455" t="inlineStr">
@@ -54059,61 +54059,61 @@
       </c>
       <c r="G1455" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>GBLS-LR263537</t>
+          <t>BLS-LR26997</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>20263323</t>
+          <t>2026891</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>٨ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1456" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>ناصر محمد ناصر آل مسلم</t>
         </is>
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1456" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1456" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>GBLS-LR263578</t>
+          <t>GBLS-LR261707</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>20263402</t>
+          <t>20262186</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>٩ - محرم - ١٤٤٨ هـ</t>
+          <t>١٧ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
@@ -54123,7 +54123,7 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1457" t="inlineStr">
@@ -54140,17 +54140,17 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>GBLS-LR264227</t>
+          <t>GBLS-LR261803</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>20263765</t>
+          <t>20263361</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٠ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -54160,7 +54160,7 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1458" t="inlineStr">
@@ -54177,17 +54177,17 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>GBLS-LR264447</t>
+          <t>GBLS-LR262615</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>20264047</t>
+          <t>20262341</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>٢٢ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - ذو الحجة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -54214,17 +54214,17 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>GBLS-LR264953</t>
+          <t>GBLS-LR263537</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>20264430</t>
+          <t>20263323</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٨ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
@@ -54232,7 +54232,11 @@
           <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
-      <c r="E1460" t="inlineStr"/>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
       <c r="F1460" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -54247,17 +54251,17 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>GBLS-LR265064</t>
+          <t>GBLS-LR263578</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>20264519</t>
+          <t>20263402</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
@@ -54284,17 +54288,17 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>GBLS-LR266387</t>
+          <t>GBLS-LR264227</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>20265632</t>
+          <t>20263765</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>١٩ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -54321,17 +54325,17 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>GBLS-LR266569</t>
+          <t>GBLS-LR264447</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>20265786</t>
+          <t>20264047</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>٢١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٢ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
@@ -54341,7 +54345,7 @@
       </c>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1463" t="inlineStr">
@@ -54358,17 +54362,17 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>GBLS-LR267898</t>
+          <t>GBLS-LR264953</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>20267572</t>
+          <t>20264430</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>١١ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
@@ -54376,14 +54380,10 @@
           <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
-      <c r="E1464" t="inlineStr">
-        <is>
-          <t>حي ظهره لبن</t>
-        </is>
-      </c>
+      <c r="E1464" t="inlineStr"/>
       <c r="F1464" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1464" t="inlineStr">
@@ -54395,17 +54395,17 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>GBLS-LR268067</t>
+          <t>GBLS-LR265064</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>20268306</t>
+          <t>20264519</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr">
@@ -54415,7 +54415,7 @@
       </c>
       <c r="E1465" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1465" t="inlineStr">
@@ -54432,27 +54432,27 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>OST-LR264090</t>
+          <t>GBLS-LR266387</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>20262152</t>
+          <t>20265632</t>
         </is>
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>١٧ - محرم - ١٤٤٨ هـ</t>
+          <t>١٩ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
         <is>
-          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1466" t="inlineStr">
@@ -54462,34 +54462,34 @@
       </c>
       <c r="G1466" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>OST-LR264772</t>
+          <t>GBLS-LR266569</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>20262152</t>
+          <t>20265786</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>٢٧ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
         <is>
-          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1467" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1467" t="inlineStr">
@@ -54499,66 +54499,66 @@
       </c>
       <c r="G1467" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>OST-LR265023</t>
+          <t>GBLS-LR267898</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>2026613</t>
+          <t>20267572</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>١١ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
         <is>
-          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1468" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1468" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>OST-LR266524</t>
+          <t>GBLS-LR268067</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>20262767</t>
+          <t>20268306</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
         <is>
-          <t>خالد شاهر بن مصلح المطيري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1469" t="inlineStr">
@@ -54573,34 +54573,34 @@
       </c>
       <c r="G1469" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OST-LR268954</t>
+          <t>OST-LR264090</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>20265645</t>
+          <t>20262152</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>مؤسسة عنوان الرفيعة للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
         </is>
       </c>
       <c r="E1470" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1470" t="inlineStr">
@@ -54617,27 +54617,27 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OST-LR269061</t>
+          <t>OST-LR264772</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>20265551</t>
+          <t>20262152</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
         <is>
-          <t>ناصر ظافر بن جديع ال فهاد</t>
+          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
         </is>
       </c>
       <c r="E1471" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1471" t="inlineStr">
@@ -54654,27 +54654,27 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>RUS-LR261413</t>
+          <t>OST-LR265023</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>2026629</t>
+          <t>2026613</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>٦ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
         <is>
-          <t>عبدالعزيز ناصر سعد السعد</t>
+          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1472" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1472" t="inlineStr">
@@ -54684,34 +54684,34 @@
       </c>
       <c r="G1472" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>RUS-LR263097</t>
+          <t>OST-LR266524</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>20262566</t>
+          <t>20262767</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>٢٩ - ذو الحجة - ١٤٤٧ هـ</t>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
         <is>
-          <t>عبدالرحمن ابراهيم عبدالعزيز العريني</t>
+          <t>خالد شاهر بن مصلح المطيري</t>
         </is>
       </c>
       <c r="E1473" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1473" t="inlineStr">
@@ -54721,71 +54721,71 @@
       </c>
       <c r="G1473" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>RUS-LR264967</t>
+          <t>OST-LR268954</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>20265645</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>مؤسسة عنوان الرفيعة للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1474" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1474" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1474" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>RUS-LR264969</t>
+          <t>OST-LR269061</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>20262723</t>
+          <t>20265551</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
         <is>
-          <t>معدى صنيتان رازن العتيبي</t>
+          <t>ناصر ظافر بن جديع ال فهاد</t>
         </is>
       </c>
       <c r="E1475" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1475" t="inlineStr">
@@ -54795,71 +54795,71 @@
       </c>
       <c r="G1475" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>RUS-LR264980</t>
+          <t>OST-LR269812</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>20261050</t>
+          <t>20264904</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>مكتب بركة عريض للعقارات</t>
         </is>
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1476" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1476" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>RUS-LR265038</t>
+          <t>RUS-LR261413</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>2026378</t>
+          <t>2026629</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>عبدالعزيز ناصر سعد السعد</t>
         </is>
       </c>
       <c r="E1477" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1477" t="inlineStr">
@@ -54876,27 +54876,27 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>RUS-LR265039</t>
+          <t>RUS-LR263097</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>2026817</t>
+          <t>20262566</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - ذو الحجة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1478" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>عبدالرحمن ابراهيم عبدالعزيز العريني</t>
         </is>
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1478" t="inlineStr">
@@ -54913,27 +54913,27 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>RUS-LR265040</t>
+          <t>RUS-LR264967</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>2026379</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1479" t="inlineStr">
@@ -54950,32 +54950,32 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>RUS-LR265045</t>
+          <t>RUS-LR264969</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>20261977</t>
+          <t>20262723</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
         <is>
-          <t>شركة ثرى الشراكة العقارية</t>
+          <t>معدى صنيتان رازن العتيبي</t>
         </is>
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1480" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1480" t="inlineStr">
@@ -54987,27 +54987,27 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>RUS-LR265080</t>
+          <t>RUS-LR264980</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>2026902</t>
+          <t>20261050</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
         <is>
-          <t>محمد عبدالله محمد الحقيل</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>حي الخزامى</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1481" t="inlineStr">
@@ -55024,27 +55024,27 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>RUS-LR265271</t>
+          <t>RUS-LR265038</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>20261204</t>
+          <t>2026378</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr">
         <is>
-          <t>سلطان سالم سلمان العميري</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1482" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1482" t="inlineStr">
@@ -55061,27 +55061,27 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>RUS-LR265311</t>
+          <t>RUS-LR265039</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>20261011</t>
+          <t>2026817</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr">
         <is>
-          <t>محمد مسفر سعد البقمي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1483" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1483" t="inlineStr">
@@ -55098,32 +55098,32 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>RUS-LR265318</t>
+          <t>RUS-LR265040</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>20261025</t>
+          <t>2026379</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
         <is>
-          <t>محمد مسفر سعد البقمي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1484" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1484" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1484" t="inlineStr">
@@ -55135,27 +55135,27 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>RUS-LR265377</t>
+          <t>RUS-LR265045</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>20262926</t>
+          <t>20261977</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
         <is>
-          <t>شركة تأصيل العقارية</t>
+          <t>شركة ثرى الشراكة العقارية</t>
         </is>
       </c>
       <c r="E1485" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1485" t="inlineStr">
@@ -55172,32 +55172,32 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>RUS-LR265391</t>
+          <t>RUS-LR265080</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>20263986</t>
+          <t>2026902</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr">
         <is>
-          <t>مؤسسة طالب مويس منيع المطيري للتطوير العقاري</t>
+          <t>محمد عبدالله محمد الحقيل</t>
         </is>
       </c>
       <c r="E1486" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي الخزامى</t>
         </is>
       </c>
       <c r="F1486" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1486" t="inlineStr">
@@ -55209,27 +55209,27 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>RUS-LR265422</t>
+          <t>RUS-LR265271</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>20263002</t>
+          <t>20261204</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
         <is>
-          <t>محمد سعد محمد الوادعي</t>
+          <t>سلطان سالم سلمان العميري</t>
         </is>
       </c>
       <c r="E1487" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1487" t="inlineStr">
@@ -55246,22 +55246,22 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>RUS-LR265483</t>
+          <t>RUS-LR265311</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>20263669</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
         <is>
-          <t>عبدالعزيز محمد حسن العتيبي</t>
+          <t>محمد مسفر سعد البقمي</t>
         </is>
       </c>
       <c r="E1488" t="inlineStr">
@@ -55283,27 +55283,27 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>RUS-LR265493</t>
+          <t>RUS-LR265318</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>20263649</t>
+          <t>20261025</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
         <is>
-          <t>وفاء عبدالله حمد المنيع</t>
+          <t>محمد مسفر سعد البقمي</t>
         </is>
       </c>
       <c r="E1489" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1489" t="inlineStr">
@@ -55320,27 +55320,27 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>RUS-LR265568</t>
+          <t>RUS-LR265377</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>20263528</t>
+          <t>20262926</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>شركة تأصيل العقارية</t>
         </is>
       </c>
       <c r="E1490" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1490" t="inlineStr">
@@ -55357,32 +55357,32 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>RUS-LR265623</t>
+          <t>RUS-LR265391</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>20263986</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>مؤسسة طالب مويس منيع المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1491" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1491" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1491" t="inlineStr">
@@ -55394,27 +55394,27 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>RUS-LR265625</t>
+          <t>RUS-LR265422</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>20261977</t>
+          <t>20263002</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr">
         <is>
-          <t>شركة ثرى الشراكة العقارية</t>
+          <t>محمد سعد محمد الوادعي</t>
         </is>
       </c>
       <c r="E1492" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1492" t="inlineStr">
@@ -55431,32 +55431,32 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>RUS-LR265709</t>
+          <t>RUS-LR265483</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>20261304</t>
+          <t>20263669</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
         <is>
-          <t>شركة فناء الإبتكار للتطوير العقاري</t>
+          <t>عبدالعزيز محمد حسن العتيبي</t>
         </is>
       </c>
       <c r="E1493" t="inlineStr">
         <is>
-          <t>حي العوالي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1493" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1493" t="inlineStr">
@@ -55468,27 +55468,27 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>RUS-LR265869</t>
+          <t>RUS-LR265493</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>20261829</t>
+          <t>20263649</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
         <is>
-          <t>منى محمدمساعد خالد الحكيم</t>
+          <t>وفاء عبدالله حمد المنيع</t>
         </is>
       </c>
       <c r="E1494" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1494" t="inlineStr">
@@ -55505,27 +55505,27 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>RUS-LR265881</t>
+          <t>RUS-LR265568</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>20262926</t>
+          <t>20263528</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
         <is>
-          <t>شركة تأصيل العقارية</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1495" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1495" t="inlineStr">
@@ -55542,22 +55542,22 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>RUS-LR265941</t>
+          <t>RUS-LR265623</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>2026241</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
         <is>
-          <t>هلال حمدان غازي العتيبي</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1496" t="inlineStr">
@@ -55567,7 +55567,7 @@
       </c>
       <c r="F1496" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1496" t="inlineStr">
@@ -55579,27 +55579,27 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>RUS-LR265989</t>
+          <t>RUS-LR265625</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>20263868</t>
+          <t>20261977</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>١٣ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
         <is>
-          <t>نايف محمد صنهات السبيعي</t>
+          <t>شركة ثرى الشراكة العقارية</t>
         </is>
       </c>
       <c r="E1497" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1497" t="inlineStr">
@@ -55616,64 +55616,64 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>RUS-LR266100</t>
+          <t>RUS-LR265709</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>20264470</t>
+          <t>20261304</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>١٤ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
         <is>
-          <t>مؤسسة جدر العربية للتطوير والاستثمار العقاري</t>
+          <t>شركة فناء الإبتكار للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>حي العريجاء الوسطى</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1498" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1498" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>RUS-LR266155</t>
+          <t>RUS-LR265869</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>2026379</t>
+          <t>20261829</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>منى محمدمساعد خالد الحكيم</t>
         </is>
       </c>
       <c r="E1499" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1499" t="inlineStr">
@@ -55690,32 +55690,32 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>RUS-LR266384</t>
+          <t>RUS-LR265881</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>20264824</t>
+          <t>20262926</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>١٩ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
         <is>
-          <t>عبدالحكيم علي عبده محمد الحكمي</t>
+          <t>شركة تأصيل العقارية</t>
         </is>
       </c>
       <c r="E1500" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1500" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1500" t="inlineStr">
@@ -55727,27 +55727,27 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>RUS-LR266540</t>
+          <t>RUS-LR265941</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>20261645</t>
+          <t>2026241</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>٢١ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr">
         <is>
-          <t>مؤسسة مباني الورود للتطوير العقاري</t>
+          <t>هلال حمدان غازي العتيبي</t>
         </is>
       </c>
       <c r="E1501" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1501" t="inlineStr">
@@ -55764,27 +55764,27 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>RUS-LR266691</t>
+          <t>RUS-LR265989</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>202517</t>
+          <t>20263868</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>٢٣ - صفر - ١٤٤٨ هـ</t>
+          <t>١٣ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr">
         <is>
-          <t>ماجد بن عبدالله نابت الشهراني</t>
+          <t>نايف محمد صنهات السبيعي</t>
         </is>
       </c>
       <c r="E1502" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1502" t="inlineStr">
@@ -55801,64 +55801,64 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>RUS-LR266771</t>
+          <t>RUS-LR266100</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>20262626</t>
+          <t>20264470</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr">
         <is>
-          <t>بزيع سليمان بزيع المبارك</t>
+          <t>مؤسسة جدر العربية للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1503" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي العريجاء الوسطى</t>
         </is>
       </c>
       <c r="F1503" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1503" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>RUS-LR266803</t>
+          <t>RUS-LR266155</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>20264988</t>
+          <t>2026379</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr">
         <is>
-          <t>سلطان بن منير بن منيف البقمي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1504" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1504" t="inlineStr">
@@ -55875,22 +55875,22 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>RUS-LR266814</t>
+          <t>RUS-LR266384</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>2026605</t>
+          <t>20264824</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٩ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>مؤسسة فهد سعود اليوسف</t>
+          <t>عبدالحكيم علي عبده محمد الحكمي</t>
         </is>
       </c>
       <c r="E1505" t="inlineStr">
@@ -55912,27 +55912,27 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>RUS-LR266930</t>
+          <t>RUS-LR266540</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>20265106</t>
+          <t>20261645</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>عبدالهادي جعفر خنثل بن شري</t>
+          <t>مؤسسة مباني الورود للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1506" t="inlineStr">
@@ -55949,27 +55949,27 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>RUS-LR266984</t>
+          <t>RUS-LR266691</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>2026902</t>
+          <t>202517</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٣ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr">
         <is>
-          <t>محمد عبدالله محمد الحقيل</t>
+          <t>ماجد بن عبدالله نابت الشهراني</t>
         </is>
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>حي الخزامى</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1507" t="inlineStr">
@@ -55979,39 +55979,39 @@
       </c>
       <c r="G1507" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>RUS-LR266991</t>
+          <t>RUS-LR266771</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>20265006</t>
+          <t>20262626</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1508" t="inlineStr">
         <is>
-          <t>شركة وتد الديار</t>
+          <t>بزيع سليمان بزيع المبارك</t>
         </is>
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1508" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1508" t="inlineStr">
@@ -56023,27 +56023,27 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>RUS-LR266993</t>
+          <t>RUS-LR266803</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>20265012</t>
+          <t>20264988</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr">
         <is>
-          <t>شركة وتد الديار</t>
+          <t>سلطان بن منير بن منيف البقمي</t>
         </is>
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1509" t="inlineStr">
@@ -56060,27 +56060,27 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>RUS-LR267452</t>
+          <t>RUS-LR266814</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>2026865</t>
+          <t>2026605</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة فهد سعود اليوسف</t>
         </is>
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1510" t="inlineStr">
@@ -56097,27 +56097,27 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>RUS-LR267541</t>
+          <t>RUS-LR266930</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>20263700</t>
+          <t>20265106</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr">
         <is>
-          <t>٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>مؤسسة نرجس المبانى للتطوير العقاري</t>
+          <t>عبدالهادي جعفر خنثل بن شري</t>
         </is>
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1511" t="inlineStr">
@@ -56134,27 +56134,27 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>RUS-LR267556</t>
+          <t>RUS-LR266984</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>20263440</t>
+          <t>2026902</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>ابراهيم فائز ابراهيم القحطاني</t>
+          <t>محمد عبدالله محمد الحقيل</t>
         </is>
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الخزامى</t>
         </is>
       </c>
       <c r="F1512" t="inlineStr">
@@ -56164,34 +56164,34 @@
       </c>
       <c r="G1512" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>RUS-LR267632</t>
+          <t>RUS-LR266991</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>2026613</t>
+          <t>20265006</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
+          <t>شركة وتد الديار</t>
         </is>
       </c>
       <c r="E1513" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1513" t="inlineStr">
@@ -56208,25 +56208,29 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>RUS-LR267647</t>
+          <t>RUS-LR266993</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>20264482</t>
+          <t>20265012</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
-          <t>عناد عاتق عيد العميرى</t>
-        </is>
-      </c>
-      <c r="E1514" t="inlineStr"/>
+          <t>شركة وتد الديار</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>حي السويدي الغربي</t>
+        </is>
+      </c>
       <c r="F1514" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56241,22 +56245,22 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>RUS-LR267651</t>
+          <t>RUS-LR267452</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>20262551</t>
+          <t>2026865</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>عناد عاتق عيد العميرى</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1515" t="inlineStr">
@@ -56278,27 +56282,27 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>RUS-LR267722</t>
+          <t>RUS-LR267541</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>20264896</t>
+          <t>20263700</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>عبدالعزيز بن على بن سمران الحربي</t>
+          <t>مؤسسة نرجس المبانى للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1516" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1516" t="inlineStr">
@@ -56315,25 +56319,29 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>RUS-LR267741</t>
+          <t>RUS-LR267556</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>20264382</t>
+          <t>20263440</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>عبدالرحمن سعود محمد الخريف</t>
-        </is>
-      </c>
-      <c r="E1517" t="inlineStr"/>
+          <t>ابراهيم فائز ابراهيم القحطاني</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>حي ضاحية نمار</t>
+        </is>
+      </c>
       <c r="F1517" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56348,27 +56356,27 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>RUS-LR267767</t>
+          <t>RUS-LR267632</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>2026613</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1518" t="inlineStr">
@@ -56385,29 +56393,25 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>RUS-LR268079</t>
+          <t>RUS-LR267647</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>2026394</t>
+          <t>20264482</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
-        </is>
-      </c>
-      <c r="E1519" t="inlineStr">
-        <is>
-          <t>حي ديراب</t>
-        </is>
-      </c>
+          <t>عناد عاتق عيد العميرى</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr"/>
       <c r="F1519" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56422,27 +56426,27 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>RUS-LR268340</t>
+          <t>RUS-LR267651</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>20264221</t>
+          <t>20262551</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>بدر محمد بن حثيري البقمي</t>
+          <t>عناد عاتق عيد العميرى</t>
         </is>
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1520" t="inlineStr">
@@ -56459,27 +56463,27 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>RUS-LR268470</t>
+          <t>RUS-LR267722</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>20261779</t>
+          <t>20264896</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>مؤسسة التطوير النموذجية للتطوير العقاري</t>
+          <t>عبدالعزيز بن على بن سمران الحربي</t>
         </is>
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1521" t="inlineStr">
@@ -56496,29 +56500,25 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>RUS-LR268532</t>
+          <t>RUS-LR267741</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>2026394</t>
+          <t>20264382</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
-        </is>
-      </c>
-      <c r="E1522" t="inlineStr">
-        <is>
-          <t>حي ديراب</t>
-        </is>
-      </c>
+          <t>عبدالرحمن سعود محمد الخريف</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr"/>
       <c r="F1522" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56533,64 +56533,64 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>RUS-LR268621</t>
+          <t>RUS-LR267767</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>20263528</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>RUS-LR268843</t>
+          <t>RUS-LR268079</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>20266365</t>
+          <t>2026394</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>خالد بن سعد بن سعود العصيمي</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1524" t="inlineStr">
@@ -56607,25 +56607,29 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>RUS-LR268863</t>
+          <t>RUS-LR268340</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>20264382</t>
+          <t>20264221</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>عبدالرحمن سعود محمد الخريف</t>
-        </is>
-      </c>
-      <c r="E1525" t="inlineStr"/>
+          <t>بدر محمد بن حثيري البقمي</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>حي ضاحية نمار</t>
+        </is>
+      </c>
       <c r="F1525" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56640,32 +56644,32 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>RUS-LR268896</t>
+          <t>RUS-LR268470</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>20261892</t>
+          <t>20261779</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>عبدالله ابن علي ابن شايع ال شفلوت</t>
+          <t>مؤسسة التطوير النموذجية للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1526" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1526" t="inlineStr">
@@ -56677,22 +56681,22 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>RUS-LR268922</t>
+          <t>RUS-LR268532</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>2026916</t>
+          <t>2026394</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>علي عائض بن علي البقمي</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1527" t="inlineStr">
@@ -56714,64 +56718,64 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>RUS-LR269043</t>
+          <t>RUS-LR268621</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>20266122</t>
+          <t>20263528</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1528" t="inlineStr">
         <is>
-          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1528" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1528" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>RUS-LR269055</t>
+          <t>RUS-LR268843</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>20263495</t>
+          <t>20266365</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>خالد بن سعد بن سعود العصيمي</t>
         </is>
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1529" t="inlineStr">
@@ -56788,32 +56792,28 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>RUS-LR269087</t>
+          <t>RUS-LR268863</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>20266955</t>
+          <t>20264382</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>نواف عبدالله حسين القحطاني</t>
-        </is>
-      </c>
-      <c r="E1530" t="inlineStr">
-        <is>
-          <t>حي طويق</t>
-        </is>
-      </c>
+          <t>عبدالرحمن سعود محمد الخريف</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr"/>
       <c r="F1530" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1530" t="inlineStr">
@@ -56825,32 +56825,32 @@
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>RUS-LR269169</t>
+          <t>RUS-LR268896</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>20266137</t>
+          <t>20261892</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>شركة رصين نجد العقارية</t>
+          <t>عبدالله ابن علي ابن شايع ال شفلوت</t>
         </is>
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1531" t="inlineStr">
         <is>
-          <t>ملغي</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1531" t="inlineStr">
@@ -56862,27 +56862,27 @@
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>RUS-LR269180</t>
+          <t>RUS-LR268922</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>20262394</t>
+          <t>2026916</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>محمد عبدالوهاب سلوم السلوم</t>
+          <t>علي عائض بن علي البقمي</t>
         </is>
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1532" t="inlineStr">
@@ -56899,32 +56899,32 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>RUS-LR269184</t>
+          <t>RUS-LR269043</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>2026734</t>
+          <t>20266122</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>مؤسسة عبدالعزيز بن جلوي بن محارب المطيري</t>
+          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
         </is>
       </c>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1533" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1533" t="inlineStr">
@@ -56936,27 +56936,27 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>RUS-LR269207</t>
+          <t>RUS-LR269055</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>20263023</t>
+          <t>20263495</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
         <is>
-          <t>عائض عبدالله مبارك القحطاني</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1534" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1534" t="inlineStr">
@@ -56966,51 +56966,51 @@
       </c>
       <c r="G1534" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>RUS-LR269208</t>
+          <t>RUS-LR269087</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>20263021</t>
+          <t>20266955</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>عائض عبدالله مبارك القحطاني</t>
+          <t>نواف عبدالله حسين القحطاني</t>
         </is>
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1535" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>RUS-LR269243</t>
+          <t>RUS-LR269169</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
@@ -57020,7 +57020,7 @@
       </c>
       <c r="C1536" t="inlineStr">
         <is>
-          <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1536" t="inlineStr">
@@ -57035,7 +57035,7 @@
       </c>
       <c r="F1536" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1536" t="inlineStr">
@@ -57047,27 +57047,27 @@
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>RUS-LR269411</t>
+          <t>RUS-LR269180</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>20267329</t>
+          <t>20262394</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>مؤسسة مجد الوفاء للتطوير العقاري</t>
+          <t>محمد عبدالوهاب سلوم السلوم</t>
         </is>
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1537" t="inlineStr">
@@ -57084,32 +57084,32 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>RUS-LR269523</t>
+          <t>RUS-LR269184</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>20263699</t>
+          <t>2026734</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>مسعود حسن بن قبحان الغامدي</t>
+          <t>مؤسسة عبدالعزيز بن جلوي بن محارب المطيري</t>
         </is>
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1538" t="inlineStr">
@@ -57121,32 +57121,32 @@
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>RUS-LR269592</t>
+          <t>RUS-LR269207</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>20262178</t>
+          <t>20263023</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>شركة إثراء الرياض العقارية</t>
+          <t>عائض عبدالله مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>حي العوالي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1539" t="inlineStr">
         <is>
-          <t>ملغي</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1539" t="inlineStr">
@@ -57158,27 +57158,27 @@
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>RUS-LR269603</t>
+          <t>RUS-LR269208</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>20264202</t>
+          <t>20263021</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>جابر علي احمد مجرشي</t>
+          <t>عائض عبدالله مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1540" t="inlineStr">
@@ -57188,39 +57188,39 @@
       </c>
       <c r="G1540" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>RUS-LR269641</t>
+          <t>RUS-LR269243</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>20263967</t>
+          <t>20266137</t>
         </is>
       </c>
       <c r="C1541" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>عبدالكريم دخيل الله خاتم السلمي</t>
+          <t>شركة رصين نجد العقارية</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1541" t="inlineStr">
@@ -57232,32 +57232,32 @@
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>RUS-LR269644</t>
+          <t>RUS-LR269411</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>20261830</t>
+          <t>20267329</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
         <is>
-          <t>مؤسسة ارض وسكن للتطوير العقاري</t>
+          <t>مؤسسة مجد الوفاء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1542" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1542" t="inlineStr">
@@ -57269,101 +57269,101 @@
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>SIP-LR264068</t>
+          <t>RUS-LR269523</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>20263876</t>
+          <t>20263699</t>
         </is>
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>١٧ - محرم - ١٤٤٨ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
         <is>
-          <t>نوره عبدالعزيز محمد العريفي</t>
+          <t>مسعود حسن بن قبحان الغامدي</t>
         </is>
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1543" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1543" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>SIP-LR264320</t>
+          <t>RUS-LR269592</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>20264534</t>
+          <t>20262178</t>
         </is>
       </c>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
-          <t>شركة مدماك الغد العقارية</t>
+          <t>شركة إثراء الرياض العقارية</t>
         </is>
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1544" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1544" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>SIP-LR264372</t>
+          <t>RUS-LR269603</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>20263907</t>
+          <t>20264202</t>
         </is>
       </c>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>٢١ - محرم - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
+          <t>جابر علي احمد مجرشي</t>
         </is>
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1545" t="inlineStr">
@@ -57373,29 +57373,29 @@
       </c>
       <c r="G1545" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>SIP-LR265231</t>
+          <t>RUS-LR269641</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>20264645</t>
+          <t>20263967</t>
         </is>
       </c>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>علي بن محمد بن مسفر الحلافي</t>
+          <t>عبدالكريم دخيل الله خاتم السلمي</t>
         </is>
       </c>
       <c r="E1546" t="inlineStr">
@@ -57405,76 +57405,76 @@
       </c>
       <c r="F1546" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1546" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>SIP-LR265499</t>
+          <t>RUS-LR269644</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>20264866</t>
+          <t>20261830</t>
         </is>
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>شركة المسكن الأمثل للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة ارض وسكن للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1547" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>SIP-LR265502</t>
+          <t>SIP-LR264068</t>
         </is>
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>20264858</t>
+          <t>20263876</t>
         </is>
       </c>
       <c r="C1548" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>١٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>سلطان ناصر زيد بن شنار</t>
+          <t>نوره عبدالعزيز محمد العريفي</t>
         </is>
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1548" t="inlineStr">
@@ -57491,27 +57491,27 @@
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>SIP-LR265662</t>
+          <t>SIP-LR264320</t>
         </is>
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>20264983</t>
+          <t>20264534</t>
         </is>
       </c>
       <c r="C1549" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1549" t="inlineStr">
         <is>
-          <t>عمر ابن عبدالعزيز ابن عبدالله الغامدي</t>
+          <t>شركة مدماك الغد العقارية</t>
         </is>
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1549" t="inlineStr">
@@ -57528,27 +57528,27 @@
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>SIP-LR265713</t>
+          <t>SIP-LR264372</t>
         </is>
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>20265038</t>
+          <t>20263907</t>
         </is>
       </c>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢١ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>فهده سفر بهيشان الحافي</t>
+          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
         </is>
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1550" t="inlineStr">
@@ -57565,27 +57565,27 @@
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>SIP-LR265893</t>
+          <t>SIP-LR265231</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>20265178</t>
+          <t>20264645</t>
         </is>
       </c>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>مؤسسة محمد علي محمد التميمي للتطوير العقاري</t>
+          <t>علي بن محمد بن مسفر الحلافي</t>
         </is>
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1551" t="inlineStr">
@@ -57602,27 +57602,27 @@
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>SIP-LR266235</t>
+          <t>SIP-LR265499</t>
         </is>
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>20265492</t>
+          <t>20264866</t>
         </is>
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>شركة المسكن الأمثل للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1552" t="inlineStr">
@@ -57639,27 +57639,27 @@
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>SIP-LR266237</t>
+          <t>SIP-LR265502</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>20265494</t>
+          <t>20264858</t>
         </is>
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>سلطان ناصر زيد بن شنار</t>
         </is>
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1553" t="inlineStr">
@@ -57676,27 +57676,27 @@
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>SIP-LR266243</t>
+          <t>SIP-LR265662</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>20265495</t>
+          <t>20264983</t>
         </is>
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>عمر ابن عبدالعزيز ابن عبدالله الغامدي</t>
         </is>
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1554" t="inlineStr">
@@ -57713,27 +57713,27 @@
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>SIP-LR266356</t>
+          <t>SIP-LR265713</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>20265660</t>
+          <t>20265038</t>
         </is>
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>١٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>شركة امثل للاستثمار</t>
+          <t>فهده سفر بهيشان الحافي</t>
         </is>
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1555" t="inlineStr">
@@ -57750,22 +57750,22 @@
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>SIP-LR266526</t>
+          <t>SIP-LR265893</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>20265751</t>
+          <t>20265178</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة محمد علي محمد التميمي للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1556" t="inlineStr">
@@ -57787,27 +57787,27 @@
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>SIP-LR266527</t>
+          <t>SIP-LR266235</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>20265752</t>
+          <t>20265492</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -57824,27 +57824,27 @@
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>SIP-LR266637</t>
+          <t>SIP-LR266237</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>20265853</t>
+          <t>20265494</t>
         </is>
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>حنان عبدالرحيم مطلق الاحمدي</t>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1558" t="inlineStr">
@@ -57861,27 +57861,27 @@
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>SIP-LR266649</t>
+          <t>SIP-LR266243</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>20265864</t>
+          <t>20265495</t>
         </is>
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>مؤسسة الوجهة الحديثة للتطوير العقاري</t>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1559" t="inlineStr">
@@ -57898,27 +57898,27 @@
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>SIP-LR266788</t>
+          <t>SIP-LR266356</t>
         </is>
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>20265977</t>
+          <t>20265660</t>
         </is>
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>عبدالعزيز مقعد مرزوق المطيري</t>
+          <t>شركة امثل للاستثمار</t>
         </is>
       </c>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1560" t="inlineStr">
@@ -57935,27 +57935,27 @@
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>SIP-LR266976</t>
+          <t>SIP-LR266526</t>
         </is>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>20266673</t>
+          <t>20265751</t>
         </is>
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>عبيد محمد مطلق العصيمي</t>
+          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1561" t="inlineStr">
@@ -57972,27 +57972,27 @@
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>SIP-LR266985</t>
+          <t>SIP-LR266527</t>
         </is>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>20266172</t>
+          <t>20265752</t>
         </is>
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>شركة ساف العقارية</t>
+          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1562" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1562" t="inlineStr">
@@ -58009,27 +58009,27 @@
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>SIP-LR267002</t>
+          <t>SIP-LR266637</t>
         </is>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>20266182</t>
+          <t>20265853</t>
         </is>
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>٢٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>شركة ساف العقارية</t>
+          <t>حنان عبدالرحيم مطلق الاحمدي</t>
         </is>
       </c>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1563" t="inlineStr">
@@ -58046,22 +58046,22 @@
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>SIP-LR267466</t>
+          <t>SIP-LR266649</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>20266601</t>
+          <t>20265864</t>
         </is>
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>شركة عمرانيات الجزيره للمقاولات</t>
+          <t>مؤسسة الوجهة الحديثة للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
@@ -58083,27 +58083,27 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>SIP-LR267636</t>
+          <t>SIP-LR266788</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>20266785</t>
+          <t>20265977</t>
         </is>
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>شركة المسمات للتطوير والاستثمار العقاري شخص واحد</t>
+          <t>عبدالعزيز مقعد مرزوق المطيري</t>
         </is>
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1565" t="inlineStr">
@@ -58120,27 +58120,27 @@
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>SIP-LR267770</t>
+          <t>SIP-LR266976</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>20266879</t>
+          <t>20266673</t>
         </is>
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>عبيد محمد مطلق العصيمي</t>
         </is>
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1566" t="inlineStr">
@@ -58157,27 +58157,27 @@
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>SIP-LR267774</t>
+          <t>SIP-LR266985</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>20266887</t>
+          <t>20266172</t>
         </is>
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>شركة ساف العقارية</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1567" t="inlineStr">
@@ -58194,27 +58194,27 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>SIP-LR267777</t>
+          <t>SIP-LR267002</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>20266896</t>
+          <t>20266182</t>
         </is>
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>شركة ساف العقارية</t>
         </is>
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1568" t="inlineStr">
@@ -58231,27 +58231,27 @@
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>SIP-LR267816</t>
+          <t>SIP-LR267466</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>20266926</t>
+          <t>20266601</t>
         </is>
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>عبدالعزيز غيث موسى الغيث</t>
+          <t>شركة عمرانيات الجزيره للمقاولات</t>
         </is>
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1569" t="inlineStr">
@@ -58268,27 +58268,27 @@
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>SIP-LR267818</t>
+          <t>SIP-LR267636</t>
         </is>
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>20266927</t>
+          <t>20266785</t>
         </is>
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+          <t>شركة المسمات للتطوير والاستثمار العقاري شخص واحد</t>
         </is>
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1570" t="inlineStr">
@@ -58305,22 +58305,22 @@
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>SIP-LR268065</t>
+          <t>SIP-LR267770</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>20267343</t>
+          <t>20266879</t>
         </is>
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>عبدالعزيز صالح مبارك الماجد</t>
+          <t>شركة حلول التطوير العقارية</t>
         </is>
       </c>
       <c r="E1571" t="inlineStr">
@@ -58342,27 +58342,27 @@
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>SIP-LR268337</t>
+          <t>SIP-LR267774</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>20267375</t>
+          <t>20266887</t>
         </is>
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>شركة الأماني العقارية (شركة شخص واحد)</t>
+          <t>شركة حلول التطوير العقارية</t>
         </is>
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1572" t="inlineStr">
@@ -58379,27 +58379,27 @@
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>SIP-LR268611</t>
+          <t>SIP-LR267777</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>20267740</t>
+          <t>20266896</t>
         </is>
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>مؤسسة أوكن للتطوير العقاري</t>
+          <t>شركة حلول التطوير العقارية</t>
         </is>
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1573" t="inlineStr">
@@ -58416,27 +58416,27 @@
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>SIP-LR269370</t>
+          <t>SIP-LR267816</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>20268256</t>
+          <t>20266926</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>محمد حمد عثمان الحسين</t>
+          <t>عبدالعزيز غيث موسى الغيث</t>
         </is>
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1574" t="inlineStr">
@@ -58453,17 +58453,17 @@
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>SIP-LR269536</t>
+          <t>SIP-LR267818</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>20268409</t>
+          <t>20266927</t>
         </is>
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -58490,35 +58490,220 @@
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
+          <t>SIP-LR268065</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>20267343</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>عبدالعزيز صالح مبارك الماجد</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>SIP-LR268337</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>20267375</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>شركة الأماني العقارية (شركة شخص واحد)</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>حي السويدي الغربي</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>SIP-LR268611</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>20267740</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>مؤسسة أوكن للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>حي ظهره لبن</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>SIP-LR269370</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>20268256</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>محمد حمد عثمان الحسين</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>حي عرقه</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>SIP-LR269536</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>20268409</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
           <t>SIP-LR269720</t>
         </is>
       </c>
-      <c r="B1576" t="inlineStr">
+      <c r="B1581" t="inlineStr">
         <is>
           <t>20268540</t>
         </is>
       </c>
-      <c r="C1576" t="inlineStr">
+      <c r="C1581" t="inlineStr">
         <is>
           <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
-      <c r="D1576" t="inlineStr">
+      <c r="D1581" t="inlineStr">
         <is>
           <t>مؤسسة عوالي الابداع للمقاولات</t>
         </is>
       </c>
-      <c r="E1576" t="inlineStr">
+      <c r="E1581" t="inlineStr">
         <is>
           <t>حي العوالي</t>
         </is>
       </c>
-      <c r="F1576" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="G1576" t="inlineStr">
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr">
         <is>
           <t>تجهيز موقع</t>
         </is>

--- a/ups_requests.xlsx
+++ b/ups_requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1581"/>
+  <dimension ref="A1:G1588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G988" t="inlineStr">
@@ -43558,7 +43558,7 @@
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1171" t="inlineStr">
@@ -43706,7 +43706,7 @@
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>قيد العمل - مشرف رخص البناء</t>
         </is>
       </c>
       <c r="G1175" t="inlineStr">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="F1187" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1187" t="inlineStr">
@@ -46884,7 +46884,7 @@
       </c>
       <c r="F1261" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1261" t="inlineStr">
@@ -47143,7 +47143,7 @@
       </c>
       <c r="F1268" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1268" t="inlineStr">
@@ -48105,7 +48105,7 @@
       </c>
       <c r="F1294" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1294" t="inlineStr">
@@ -50510,7 +50510,7 @@
       </c>
       <c r="F1359" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1359" t="inlineStr">
@@ -50991,7 +50991,7 @@
       </c>
       <c r="F1372" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1372" t="inlineStr">
@@ -51065,7 +51065,7 @@
       </c>
       <c r="F1374" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1374" t="inlineStr">
@@ -51410,12 +51410,12 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>BLS-LR269295</t>
+          <t>BLS-LR269294</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>20268191</t>
+          <t>20268627</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr">
@@ -51425,17 +51425,17 @@
       </c>
       <c r="D1384" t="inlineStr">
         <is>
-          <t>شركة إشراقة الفن العقارية شخص واحد</t>
+          <t>عبدالعزيز بن عبدالله بن عبدالعزيز الدعيلج</t>
         </is>
       </c>
       <c r="E1384" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1384" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1384" t="inlineStr">
@@ -51447,12 +51447,12 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>BLS-LR269306</t>
+          <t>BLS-LR269295</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>20268244</t>
+          <t>20268191</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr">
@@ -51462,17 +51462,17 @@
       </c>
       <c r="D1385" t="inlineStr">
         <is>
-          <t>فهد مشبب عبدالرحمن الخنفري</t>
+          <t>شركة إشراقة الفن العقارية شخص واحد</t>
         </is>
       </c>
       <c r="E1385" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1385" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1385" t="inlineStr">
@@ -51484,12 +51484,12 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>BLS-LR269316</t>
+          <t>BLS-LR269306</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>20268334</t>
+          <t>20268244</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr">
@@ -51499,12 +51499,12 @@
       </c>
       <c r="D1386" t="inlineStr">
         <is>
-          <t>شركة معالي العقارية شركة شخص واحد</t>
+          <t>فهد مشبب عبدالرحمن الخنفري</t>
         </is>
       </c>
       <c r="E1386" t="inlineStr">
         <is>
-          <t>حي السويدي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1386" t="inlineStr">
@@ -51521,10 +51521,14 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>BLS-LR269318</t>
-        </is>
-      </c>
-      <c r="B1387" t="inlineStr"/>
+          <t>BLS-LR269316</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>20268334</t>
+        </is>
+      </c>
       <c r="C1387" t="inlineStr">
         <is>
           <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
@@ -51532,7 +51536,7 @@
       </c>
       <c r="D1387" t="inlineStr">
         <is>
-          <t>شركة عالم المباني للتطوير العقاري</t>
+          <t>شركة معالي العقارية شركة شخص واحد</t>
         </is>
       </c>
       <c r="E1387" t="inlineStr">
@@ -51542,7 +51546,7 @@
       </c>
       <c r="F1387" t="inlineStr">
         <is>
-          <t>ملغي</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1387" t="inlineStr">
@@ -51554,14 +51558,10 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>BLS-LR269319</t>
-        </is>
-      </c>
-      <c r="B1388" t="inlineStr">
-        <is>
-          <t>20268206</t>
-        </is>
-      </c>
+          <t>BLS-LR269318</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr"/>
       <c r="C1388" t="inlineStr">
         <is>
           <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="F1388" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1388" t="inlineStr">
@@ -51591,32 +51591,32 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>BLS-LR269338</t>
+          <t>BLS-LR269319</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>20268281</t>
+          <t>20268206</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr">
         <is>
-          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1389" t="inlineStr">
         <is>
-          <t>نواف عبدالعزيز بن عبدالله العريفي</t>
+          <t>شركة عالم المباني للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي السويدي</t>
         </is>
       </c>
       <c r="F1389" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1389" t="inlineStr">
@@ -51628,10 +51628,14 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>BLS-LR269354</t>
-        </is>
-      </c>
-      <c r="B1390" t="inlineStr"/>
+          <t>BLS-LR269338</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>20268281</t>
+        </is>
+      </c>
       <c r="C1390" t="inlineStr">
         <is>
           <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
@@ -51639,17 +51643,17 @@
       </c>
       <c r="D1390" t="inlineStr">
         <is>
-          <t>محمد حمد عثمان الحسين</t>
+          <t>نواف عبدالعزيز بن عبدالله العريفي</t>
         </is>
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1390" t="inlineStr">
         <is>
-          <t>ملغي</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1390" t="inlineStr">
@@ -51661,14 +51665,10 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>BLS-LR269359</t>
-        </is>
-      </c>
-      <c r="B1391" t="inlineStr">
-        <is>
-          <t>20268429</t>
-        </is>
-      </c>
+          <t>BLS-LR269354</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr"/>
       <c r="C1391" t="inlineStr">
         <is>
           <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
@@ -51676,17 +51676,17 @@
       </c>
       <c r="D1391" t="inlineStr">
         <is>
-          <t>محمد احمد محمد القحطاني</t>
+          <t>محمد حمد عثمان الحسين</t>
         </is>
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1391" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1391" t="inlineStr">
@@ -51698,12 +51698,12 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>BLS-LR269360</t>
+          <t>BLS-LR269359</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>20268276</t>
+          <t>20268429</t>
         </is>
       </c>
       <c r="C1392" t="inlineStr">
@@ -51723,7 +51723,7 @@
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1392" t="inlineStr">
@@ -51735,12 +51735,12 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>BLS-LR269361</t>
+          <t>BLS-LR269360</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>20268240</t>
+          <t>20268276</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr">
@@ -51750,7 +51750,7 @@
       </c>
       <c r="D1393" t="inlineStr">
         <is>
-          <t>شجاع راشد بن محمد القحطانى</t>
+          <t>محمد احمد محمد القحطاني</t>
         </is>
       </c>
       <c r="E1393" t="inlineStr">
@@ -51760,7 +51760,7 @@
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1393" t="inlineStr">
@@ -51772,12 +51772,12 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>BLS-LR269367</t>
+          <t>BLS-LR269361</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>20268247</t>
+          <t>20268240</t>
         </is>
       </c>
       <c r="C1394" t="inlineStr">
@@ -51787,17 +51787,17 @@
       </c>
       <c r="D1394" t="inlineStr">
         <is>
-          <t>شركة الأفق الشمالي للتطوير العقاري</t>
+          <t>شجاع راشد بن محمد القحطانى</t>
         </is>
       </c>
       <c r="E1394" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1394" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1394" t="inlineStr">
@@ -51809,32 +51809,32 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>BLS-LR26937</t>
+          <t>BLS-LR269367</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>2026817</t>
+          <t>20268247</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1395" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>شركة الأفق الشمالي للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1395" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1395" t="inlineStr">
@@ -51846,32 +51846,32 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>BLS-LR269372</t>
+          <t>BLS-LR26937</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>20268254</t>
+          <t>2026817</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1396" t="inlineStr">
         <is>
-          <t>محمد احمد محمد القحطاني</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1396" t="inlineStr">
@@ -51883,12 +51883,12 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>BLS-LR269385</t>
+          <t>BLS-LR269372</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>20268550</t>
+          <t>20268254</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr">
@@ -51898,17 +51898,17 @@
       </c>
       <c r="D1397" t="inlineStr">
         <is>
-          <t>منصور حمد عبدالله الصالح</t>
+          <t>محمد احمد محمد القحطاني</t>
         </is>
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
@@ -51920,12 +51920,12 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>BLS-LR269386</t>
+          <t>BLS-LR269385</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>20268274</t>
+          <t>20268550</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr">
@@ -51935,7 +51935,7 @@
       </c>
       <c r="D1398" t="inlineStr">
         <is>
-          <t>ابراهيم بن عبدالله بن موسى الحمودي</t>
+          <t>منصور حمد عبدالله الصالح</t>
         </is>
       </c>
       <c r="E1398" t="inlineStr">
@@ -51945,7 +51945,7 @@
       </c>
       <c r="F1398" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1398" t="inlineStr">
@@ -51957,12 +51957,12 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>BLS-LR269392</t>
+          <t>BLS-LR269386</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>20268268</t>
+          <t>20268274</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr">
@@ -51972,17 +51972,17 @@
       </c>
       <c r="D1399" t="inlineStr">
         <is>
-          <t>عبدالله بن شباب بن عيد العصيمي</t>
+          <t>ابراهيم بن عبدالله بن موسى الحمودي</t>
         </is>
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1399" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1399" t="inlineStr">
@@ -51994,22 +51994,22 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>BLS-LR2694</t>
+          <t>BLS-LR269392</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>202695</t>
+          <t>20268268</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>٧ - شعبان - ١٤٤٧ هـ</t>
+          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1400" t="inlineStr">
         <is>
-          <t>شركة ألوينر ريزيدنس</t>
+          <t>عبدالله بن شباب بن عيد العصيمي</t>
         </is>
       </c>
       <c r="E1400" t="inlineStr">
@@ -52019,7 +52019,7 @@
       </c>
       <c r="F1400" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1400" t="inlineStr">
@@ -52031,32 +52031,32 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>BLS-LR269407</t>
+          <t>BLS-LR2694</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>20268601</t>
+          <t>202695</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٧ - شعبان - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1401" t="inlineStr">
         <is>
-          <t>عبدالله محمد علي بن عون</t>
+          <t>شركة ألوينر ريزيدنس</t>
         </is>
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1401" t="inlineStr">
@@ -52068,12 +52068,12 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>BLS-LR269415</t>
+          <t>BLS-LR269407</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>20268292</t>
+          <t>20268601</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr">
@@ -52083,17 +52083,17 @@
       </c>
       <c r="D1402" t="inlineStr">
         <is>
-          <t>محمد عبيد علي القحطاني</t>
+          <t>عبدالله محمد علي بن عون</t>
         </is>
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1402" t="inlineStr">
@@ -52105,12 +52105,12 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>BLS-LR269418</t>
+          <t>BLS-LR269415</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>20268471</t>
+          <t>20268292</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr">
@@ -52120,12 +52120,12 @@
       </c>
       <c r="D1403" t="inlineStr">
         <is>
-          <t>عبدالله محمد احمد القرني</t>
+          <t>محمد عبيد علي القحطاني</t>
         </is>
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1403" t="inlineStr">
@@ -52142,22 +52142,22 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>BLS-LR26943</t>
+          <t>BLS-LR269418</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>2026829</t>
+          <t>20268471</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1404" t="inlineStr">
         <is>
-          <t>علي سعيد بن صنيتان المطيري</t>
+          <t>عبدالله محمد احمد القرني</t>
         </is>
       </c>
       <c r="E1404" t="inlineStr">
@@ -52167,7 +52167,7 @@
       </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1404" t="inlineStr">
@@ -52179,32 +52179,32 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>BLS-LR269444</t>
+          <t>BLS-LR26943</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>20268324</t>
+          <t>2026829</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1405" t="inlineStr">
         <is>
-          <t>مؤسسة مشارف المنزل للتجارة</t>
+          <t>علي سعيد بن صنيتان المطيري</t>
         </is>
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1405" t="inlineStr">
@@ -52216,12 +52216,12 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>BLS-LR269447</t>
+          <t>BLS-LR269444</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>20268316</t>
+          <t>20268324</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr">
@@ -52231,17 +52231,17 @@
       </c>
       <c r="D1406" t="inlineStr">
         <is>
-          <t>شركة مدينة الضباب للتطوير العقاري</t>
+          <t>مؤسسة مشارف المنزل للتجارة</t>
         </is>
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1406" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1406" t="inlineStr">
@@ -52253,27 +52253,27 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>BLS-LR26945</t>
+          <t>BLS-LR269447</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>2026950</t>
+          <t>20268316</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
         <is>
-          <t>ناصر عبدالله حجيلان الشيباني</t>
+          <t>شركة مدينة الضباب للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1407" t="inlineStr">
@@ -52290,32 +52290,32 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>BLS-LR269453</t>
+          <t>BLS-LR26945</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>20268319</t>
+          <t>2026950</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1408" t="inlineStr">
         <is>
-          <t>علي محمد علي الأسمري</t>
+          <t>ناصر عبدالله حجيلان الشيباني</t>
         </is>
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1408" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1408" t="inlineStr">
@@ -52327,22 +52327,22 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>BLS-LR26946</t>
+          <t>BLS-LR269453</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>2026824</t>
+          <t>20268319</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
         <is>
-          <t>سلطان مبارك بن مفلح القحطاني</t>
+          <t>علي محمد علي الأسمري</t>
         </is>
       </c>
       <c r="E1409" t="inlineStr">
@@ -52352,7 +52352,7 @@
       </c>
       <c r="F1409" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1409" t="inlineStr">
@@ -52364,27 +52364,27 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>BLS-LR269476</t>
+          <t>BLS-LR26946</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>20268371</t>
+          <t>2026824</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr">
         <is>
-          <t>وائل فائز رفدان الدوسري</t>
+          <t>سلطان مبارك بن مفلح القحطاني</t>
         </is>
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1410" t="inlineStr">
@@ -52401,27 +52401,27 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>BLS-LR26949</t>
+          <t>BLS-LR269476</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>2026827</t>
+          <t>20268371</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr">
         <is>
-          <t>سلطان مبارك بن مفلح القحطاني</t>
+          <t>وائل فائز رفدان الدوسري</t>
         </is>
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1411" t="inlineStr">
@@ -52438,22 +52438,22 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>BLS-LR269495</t>
+          <t>BLS-LR26949</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>20268370</t>
+          <t>2026827</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
         <is>
-          <t>مؤسسة وهج الجوهرة للتطوير والاستثمار العقاري</t>
+          <t>سلطان مبارك بن مفلح القحطاني</t>
         </is>
       </c>
       <c r="E1412" t="inlineStr">
@@ -52475,32 +52475,32 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>BLS-LR26950</t>
+          <t>BLS-LR269495</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>2026830</t>
+          <t>20268370</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>مؤسسة وهج الجوهرة للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1413" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1413" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1413" t="inlineStr">
@@ -52512,22 +52512,22 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>BLS-LR269500</t>
+          <t>BLS-LR26950</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>20268413</t>
+          <t>2026830</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr">
         <is>
-          <t>مسفر صالح عبدالله الدوسري</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1414" t="inlineStr">
@@ -52537,7 +52537,7 @@
       </c>
       <c r="F1414" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1414" t="inlineStr">
@@ -52549,12 +52549,12 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>BLS-LR269507</t>
+          <t>BLS-LR269500</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>20268367</t>
+          <t>20268413</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
@@ -52564,12 +52564,12 @@
       </c>
       <c r="D1415" t="inlineStr">
         <is>
-          <t>رشيد عبدالله سعيد السملق</t>
+          <t>مسفر صالح عبدالله الدوسري</t>
         </is>
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1415" t="inlineStr">
@@ -52586,32 +52586,32 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>BLS-LR26951</t>
+          <t>BLS-LR269507</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>2026832</t>
+          <t>20268367</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>١٩ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr">
         <is>
-          <t>ذعار عايض ذعار العجمي</t>
+          <t>رشيد عبدالله سعيد السملق</t>
         </is>
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1416" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1416" t="inlineStr">
@@ -52623,32 +52623,32 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>BLS-LR269525</t>
+          <t>BLS-LR26951</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>20268585</t>
+          <t>2026832</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٩ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
         <is>
-          <t>مؤسسة زبر للتطوير العقاري</t>
+          <t>ذعار عايض ذعار العجمي</t>
         </is>
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1417" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1417" t="inlineStr">
@@ -52660,12 +52660,12 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>BLS-LR269544</t>
+          <t>BLS-LR269525</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>20268414</t>
+          <t>20268585</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
@@ -52675,17 +52675,17 @@
       </c>
       <c r="D1418" t="inlineStr">
         <is>
-          <t>مؤسسة مبارك عبدالله بن مبارك آل مغيره للتطوير العقاري</t>
+          <t>مؤسسة زبر للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1418" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1418" t="inlineStr">
@@ -52697,12 +52697,12 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>BLS-LR269547</t>
+          <t>BLS-LR269544</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>20268421</t>
+          <t>20268414</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
@@ -52712,12 +52712,12 @@
       </c>
       <c r="D1419" t="inlineStr">
         <is>
-          <t>شركة استدامة الأعمال المالية</t>
+          <t>مؤسسة مبارك عبدالله بن مبارك آل مغيره للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>حي ظهره البديعه</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1419" t="inlineStr">
@@ -52734,32 +52734,32 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>BLS-LR26955</t>
+          <t>BLS-LR269547</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>20261076</t>
+          <t>20268421</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
         <is>
-          <t>عبير عبدالعزيز عبدالله الصالح</t>
+          <t>شركة استدامة الأعمال المالية</t>
         </is>
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ظهره البديعه</t>
         </is>
       </c>
       <c r="F1420" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1420" t="inlineStr">
@@ -52771,27 +52771,27 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>BLS-LR269556</t>
+          <t>BLS-LR26955</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>20268422</t>
+          <t>20261076</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1421" t="inlineStr">
         <is>
-          <t>عطيه علي عطيه الغامدي</t>
+          <t>عبير عبدالعزيز عبدالله الصالح</t>
         </is>
       </c>
       <c r="E1421" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1421" t="inlineStr">
@@ -52808,12 +52808,12 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>BLS-LR269564</t>
+          <t>BLS-LR269556</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>20268485</t>
+          <t>20268422</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr">
@@ -52823,17 +52823,17 @@
       </c>
       <c r="D1422" t="inlineStr">
         <is>
-          <t>سلطان سرحان محمد مرشد</t>
+          <t>عطيه علي عطيه الغامدي</t>
         </is>
       </c>
       <c r="E1422" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1422" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1422" t="inlineStr">
@@ -52845,12 +52845,12 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>BLS-LR269566</t>
+          <t>BLS-LR269564</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>20268425</t>
+          <t>20268485</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr">
@@ -52860,17 +52860,17 @@
       </c>
       <c r="D1423" t="inlineStr">
         <is>
-          <t>محمد خالد بن محيل المطيري</t>
+          <t>سلطان سرحان محمد مرشد</t>
         </is>
       </c>
       <c r="E1423" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1423" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1423" t="inlineStr">
@@ -52882,12 +52882,12 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>BLS-LR269570</t>
+          <t>BLS-LR269566</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>20268435</t>
+          <t>20268425</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr">
@@ -52897,12 +52897,12 @@
       </c>
       <c r="D1424" t="inlineStr">
         <is>
-          <t>شجاع نهار نهير العميري</t>
+          <t>محمد خالد بن محيل المطيري</t>
         </is>
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1424" t="inlineStr">
@@ -52919,12 +52919,12 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>BLS-LR269577</t>
+          <t>BLS-LR269570</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>20268439</t>
+          <t>20268435</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
@@ -52934,17 +52934,17 @@
       </c>
       <c r="D1425" t="inlineStr">
         <is>
-          <t>سبيل جودالله بنيان المطيري</t>
+          <t>شجاع نهار نهير العميري</t>
         </is>
       </c>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1425" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1425" t="inlineStr">
@@ -52956,27 +52956,27 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>BLS-LR26958</t>
+          <t>BLS-LR269577</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>2026836</t>
+          <t>20268439</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
         <is>
-          <t>ذعار عايض ذعار العجمي</t>
+          <t>سبيل جودالله بنيان المطيري</t>
         </is>
       </c>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1426" t="inlineStr">
@@ -52993,32 +52993,32 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>BLS-LR269597</t>
+          <t>BLS-LR26958</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>20268462</t>
+          <t>2026836</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
         <is>
-          <t>الجمعية الدعوية للصم</t>
+          <t>ذعار عايض ذعار العجمي</t>
         </is>
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1427" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1427" t="inlineStr">
@@ -53030,12 +53030,12 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>BLS-LR269602</t>
+          <t>BLS-LR269597</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>20268466</t>
+          <t>20268462</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr">
@@ -53045,7 +53045,7 @@
       </c>
       <c r="D1428" t="inlineStr">
         <is>
-          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+          <t>الجمعية الدعوية للصم</t>
         </is>
       </c>
       <c r="E1428" t="inlineStr">
@@ -53067,12 +53067,12 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>BLS-LR269608</t>
+          <t>BLS-LR269602</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>20268469</t>
+          <t>20268466</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
@@ -53082,7 +53082,7 @@
       </c>
       <c r="D1429" t="inlineStr">
         <is>
-          <t>فيصل بن سلطان بن فيصل آل سعود</t>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1429" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="F1429" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1429" t="inlineStr">
@@ -53104,12 +53104,12 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>BLS-LR269617</t>
+          <t>BLS-LR269608</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>20268476</t>
+          <t>20268469</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr">
@@ -53119,12 +53119,12 @@
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>مؤسسة فناء الريحان للتطوير العقاري</t>
+          <t>فيصل بن سلطان بن فيصل آل سعود</t>
         </is>
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1430" t="inlineStr">
@@ -53141,12 +53141,12 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>BLS-LR269630</t>
+          <t>BLS-LR269617</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>20268486</t>
+          <t>20268476</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr">
@@ -53156,17 +53156,17 @@
       </c>
       <c r="D1431" t="inlineStr">
         <is>
-          <t>مناحي بن مطلق بن مطير الغامدي</t>
+          <t>مؤسسة فناء الريحان للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1431" t="inlineStr">
         <is>
-          <t>بانتظار السداد</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1431" t="inlineStr">
@@ -53178,12 +53178,12 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>BLS-LR269635</t>
+          <t>BLS-LR269630</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>20268494</t>
+          <t>20268486</t>
         </is>
       </c>
       <c r="C1432" t="inlineStr">
@@ -53193,7 +53193,7 @@
       </c>
       <c r="D1432" t="inlineStr">
         <is>
-          <t>مشعل شليل بن حبيب المطيري</t>
+          <t>مناحي بن مطلق بن مطير الغامدي</t>
         </is>
       </c>
       <c r="E1432" t="inlineStr">
@@ -53215,32 +53215,32 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>BLS-LR269679</t>
+          <t>BLS-LR269635</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>20268519</t>
+          <t>20268494</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1433" t="inlineStr">
         <is>
-          <t>شركة واعد العقارية</t>
+          <t>مشعل شليل بن حبيب المطيري</t>
         </is>
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1433" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1433" t="inlineStr">
@@ -53252,32 +53252,32 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>BLS-LR26968</t>
+          <t>BLS-LR269679</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>20261517</t>
+          <t>20268519</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
         <is>
-          <t>حراز سعيد عايض العتيبي</t>
+          <t>شركة واعد العقارية</t>
         </is>
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1434" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1434" t="inlineStr">
@@ -53289,12 +53289,12 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>BLS-LR26969</t>
+          <t>BLS-LR26968</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>2026858</t>
+          <t>20261517</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
@@ -53304,7 +53304,7 @@
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>مؤسسة شوق حميد المطيري للتطوير العقاري</t>
+          <t>حراز سعيد عايض العتيبي</t>
         </is>
       </c>
       <c r="E1435" t="inlineStr">
@@ -53314,7 +53314,7 @@
       </c>
       <c r="F1435" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1435" t="inlineStr">
@@ -53326,32 +53326,32 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>BLS-LR269692</t>
+          <t>BLS-LR26969</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>20268517</t>
+          <t>2026858</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
         <is>
-          <t>عبدالرحمن عثمان محمد العياف</t>
+          <t>مؤسسة شوق حميد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>حي العوالي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1436" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1436" t="inlineStr">
@@ -53363,32 +53363,32 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>BLS-LR26971</t>
+          <t>BLS-LR269692</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>20261495</t>
+          <t>20268517</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">
         <is>
-          <t>مؤسسة قدم العقارية</t>
+          <t>عبدالرحمن عثمان محمد العياف</t>
         </is>
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1437" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1437" t="inlineStr">
@@ -53400,12 +53400,12 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>BLS-LR26972</t>
+          <t>BLS-LR26971</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>2026857</t>
+          <t>20261495</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="D1438" t="inlineStr">
         <is>
-          <t>شركة اسرار العمار للتطوير العقاري</t>
+          <t>مؤسسة قدم العقارية</t>
         </is>
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1438" t="inlineStr">
@@ -53437,32 +53437,32 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>BLS-LR269723</t>
+          <t>BLS-LR26972</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>20268535</t>
+          <t>2026857</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1439" t="inlineStr">
         <is>
-          <t>شديد حمد مبارك القحطاني</t>
+          <t>شركة اسرار العمار للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1439" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1439" t="inlineStr">
@@ -53474,32 +53474,32 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>BLS-LR26973</t>
+          <t>BLS-LR269723</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>2026865</t>
+          <t>20268535</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1440" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>شديد حمد مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1440" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1440" t="inlineStr">
@@ -53511,32 +53511,32 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>BLS-LR269747</t>
+          <t>BLS-LR26973</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>20268597</t>
+          <t>2026865</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
         <is>
-          <t>فالح ذعار فنيس القحطاني</t>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>حي العريجاء</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1441" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1441" t="inlineStr">
@@ -53548,12 +53548,12 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>BLS-LR269758</t>
+          <t>BLS-LR269747</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>20268557</t>
+          <t>20268597</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr">
@@ -53563,17 +53563,17 @@
       </c>
       <c r="D1442" t="inlineStr">
         <is>
-          <t>مؤسسة عبدالرحمن على عبدالعزيز المغامس للتطوير والاستثمار العقاري</t>
+          <t>فالح ذعار فنيس القحطاني</t>
         </is>
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي العريجاء</t>
         </is>
       </c>
       <c r="F1442" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1442" t="inlineStr">
@@ -53585,12 +53585,12 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>BLS-LR269773</t>
+          <t>BLS-LR269758</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>20268581</t>
+          <t>20268557</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr">
@@ -53600,17 +53600,17 @@
       </c>
       <c r="D1443" t="inlineStr">
         <is>
-          <t>بدريه فلاح عبدالعزيز العريفي</t>
+          <t>مؤسسة عبدالرحمن على عبدالعزيز المغامس للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1443" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1443" t="inlineStr">
@@ -53622,12 +53622,12 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>BLS-LR269774</t>
+          <t>BLS-LR269767</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>20268568</t>
+          <t>20268660</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr">
@@ -53637,12 +53637,12 @@
       </c>
       <c r="D1444" t="inlineStr">
         <is>
-          <t>غانم حمود غانم العتيبي</t>
+          <t>شركة الصروح المتحدة للعقارات</t>
         </is>
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1444" t="inlineStr">
@@ -53659,12 +53659,12 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>BLS-LR269776</t>
+          <t>BLS-LR269773</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>20268570</t>
+          <t>20268581</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr">
@@ -53674,17 +53674,17 @@
       </c>
       <c r="D1445" t="inlineStr">
         <is>
-          <t>ناصر علي ناصر القحطاني</t>
+          <t>بدريه فلاح عبدالعزيز العريفي</t>
         </is>
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1445" t="inlineStr">
@@ -53696,32 +53696,32 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>BLS-LR26978</t>
+          <t>BLS-LR269774</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>2026863</t>
+          <t>20268568</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
         <is>
-          <t>مؤسسة اجمل القصور للتطوير العقاري</t>
+          <t>غانم حمود غانم العتيبي</t>
         </is>
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1446" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1446" t="inlineStr">
@@ -53733,12 +53733,12 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>BLS-LR269783</t>
+          <t>BLS-LR269776</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>20268574</t>
+          <t>20268570</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr">
@@ -53758,7 +53758,7 @@
       </c>
       <c r="F1447" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1447" t="inlineStr">
@@ -53770,32 +53770,32 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>BLS-LR269791</t>
+          <t>BLS-LR26978</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>20268583</t>
+          <t>2026863</t>
         </is>
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
         <is>
-          <t>حسن معيض حسن الشهري</t>
+          <t>مؤسسة اجمل القصور للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1448" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1448" t="inlineStr">
@@ -53807,12 +53807,12 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>BLS-LR269796</t>
+          <t>BLS-LR269783</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>20268595</t>
+          <t>20268574</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr">
@@ -53822,17 +53822,17 @@
       </c>
       <c r="D1449" t="inlineStr">
         <is>
-          <t>فهده فيحان دويريج العتيبي</t>
+          <t>ناصر علي ناصر القحطاني</t>
         </is>
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1449" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1449" t="inlineStr">
@@ -53844,12 +53844,12 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>BLS-LR269798</t>
+          <t>BLS-LR269791</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>20268589</t>
+          <t>20268583</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr">
@@ -53859,12 +53859,12 @@
       </c>
       <c r="D1450" t="inlineStr">
         <is>
-          <t>عبدالرحمن خلوفه عوضه الشهري</t>
+          <t>حسن معيض حسن الشهري</t>
         </is>
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1450" t="inlineStr">
@@ -53881,22 +53881,22 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>BLS-LR269807</t>
+          <t>BLS-LR269796</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>20268599</t>
+          <t>20268595</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
         <is>
-          <t>شركة مدماك الغد العقارية</t>
+          <t>فهده فيحان دويريج العتيبي</t>
         </is>
       </c>
       <c r="E1451" t="inlineStr">
@@ -53906,7 +53906,7 @@
       </c>
       <c r="F1451" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1451" t="inlineStr">
@@ -53918,32 +53918,32 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>BLS-LR26981</t>
+          <t>BLS-LR269798</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>2026867</t>
+          <t>20268589</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
+          <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
         <is>
-          <t>جابر عبدالله ناصر الدخيل</t>
+          <t>عبدالرحمن خلوفه عوضه الشهري</t>
         </is>
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1452" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1452" t="inlineStr">
@@ -53955,32 +53955,32 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>BLS-LR26993</t>
+          <t>BLS-LR269807</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>2026886</t>
+          <t>20268599</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
         <is>
-          <t>شركة اتمام البناء للتطوير العقاري شركة شخص واحد</t>
+          <t>شركة مدماك الغد العقارية</t>
         </is>
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1453" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1453" t="inlineStr">
@@ -53992,32 +53992,32 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>BLS-LR26994</t>
+          <t>BLS-LR26981</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>2026885</t>
+          <t>2026867</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٢٠ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
         <is>
-          <t>مؤسسة ركاز الطيب</t>
+          <t>جابر عبدالله ناصر الدخيل</t>
         </is>
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1454" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1454" t="inlineStr">
@@ -54029,32 +54029,32 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>BLS-LR26995</t>
+          <t>BLS-LR269818</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>2026888</t>
+          <t>20268614</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
         <is>
-          <t>شركة حمد محمد بن سعيدان العقارية</t>
+          <t>محمد علي محمد بن عون</t>
         </is>
       </c>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1455" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>بانتظار السداد</t>
         </is>
       </c>
       <c r="G1455" t="inlineStr">
@@ -54066,32 +54066,32 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>BLS-LR26997</t>
+          <t>BLS-LR269824</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>2026891</t>
+          <t>20268615</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>٢١ - شوال - ١٤٤٧ هـ</t>
+          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1456" t="inlineStr">
         <is>
-          <t>ناصر محمد ناصر آل مسلم</t>
+          <t>جوزاء عبدالله عبدالعزيز الفليج</t>
         </is>
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1456" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1456" t="inlineStr">
@@ -54103,22 +54103,22 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>GBLS-LR261707</t>
+          <t>BLS-LR269847</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>20262186</t>
+          <t>20268635</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>١٧ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>عبدالعزيز عبدالله حمد المواش</t>
         </is>
       </c>
       <c r="E1457" t="inlineStr">
@@ -54128,39 +54128,39 @@
       </c>
       <c r="F1457" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1457" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>GBLS-LR261803</t>
+          <t>BLS-LR269856</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>20263361</t>
+          <t>114470000037579</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>٢٠ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>٢١ - ذو الحجة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>عبدالرحمن عبدالعزيز الحيدر</t>
         </is>
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1458" t="inlineStr">
@@ -54170,34 +54170,34 @@
       </c>
       <c r="G1458" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>GBLS-LR262615</t>
+          <t>BLS-LR269868</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>20262341</t>
+          <t>114470000032410</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>٢١ - ذو الحجة - ١٤٤٧ هـ</t>
+          <t>١٨ - رمضان - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>عدنان ابراهيم عبدالله الصانع</t>
         </is>
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1459" t="inlineStr">
@@ -54207,29 +54207,29 @@
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>GBLS-LR263537</t>
+          <t>BLS-LR26993</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>20263323</t>
+          <t>2026886</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>٨ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>شركة اتمام البناء للتطوير العقاري شركة شخص واحد</t>
         </is>
       </c>
       <c r="E1460" t="inlineStr">
@@ -54244,71 +54244,71 @@
       </c>
       <c r="G1460" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>GBLS-LR263578</t>
+          <t>BLS-LR26994</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>20263402</t>
+          <t>2026885</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>مؤسسة ركاز الطيب</t>
         </is>
       </c>
       <c r="E1461" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1461" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1461" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>GBLS-LR264227</t>
+          <t>BLS-LR26995</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>20263765</t>
+          <t>2026888</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>شركة حمد محمد بن سعيدان العقارية</t>
         </is>
       </c>
       <c r="E1462" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1462" t="inlineStr">
@@ -54318,61 +54318,61 @@
       </c>
       <c r="G1462" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>GBLS-LR264447</t>
+          <t>BLS-LR26997</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>20264047</t>
+          <t>2026891</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>٢٢ - محرم - ١٤٤٨ هـ</t>
+          <t>٢١ - شوال - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr">
         <is>
-          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+          <t>ناصر محمد ناصر آل مسلم</t>
         </is>
       </c>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1463" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1463" t="inlineStr">
         <is>
-          <t>اصدار رخصة بناء حكومي</t>
+          <t>اصدار رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>GBLS-LR264953</t>
+          <t>GBLS-LR261707</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>20264430</t>
+          <t>20262186</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>١٧ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
@@ -54380,7 +54380,11 @@
           <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
-      <c r="E1464" t="inlineStr"/>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
       <c r="F1464" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -54395,17 +54399,17 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>GBLS-LR265064</t>
+          <t>GBLS-LR261803</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>20264519</t>
+          <t>20263361</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr">
@@ -54432,17 +54436,17 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>GBLS-LR266387</t>
+          <t>GBLS-LR262615</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>20265632</t>
+          <t>20262341</t>
         </is>
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>١٩ - صفر - ١٤٤٨ هـ</t>
+          <t>٢١ - ذو الحجة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
@@ -54452,7 +54456,7 @@
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1466" t="inlineStr">
@@ -54469,17 +54473,17 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>GBLS-LR266569</t>
+          <t>GBLS-LR263537</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>20265786</t>
+          <t>20263323</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>٢١ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
@@ -54489,7 +54493,7 @@
       </c>
       <c r="E1467" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1467" t="inlineStr">
@@ -54506,17 +54510,17 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>GBLS-LR267898</t>
+          <t>GBLS-LR263578</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>20267572</t>
+          <t>20263402</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>١١ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -54526,12 +54530,12 @@
       </c>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1468" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1468" t="inlineStr">
@@ -54543,17 +54547,17 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>GBLS-LR268067</t>
+          <t>GBLS-LR264227</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>20268306</t>
+          <t>20263765</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
@@ -54580,27 +54584,27 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>OST-LR264090</t>
+          <t>GBLS-LR264447</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>20262152</t>
+          <t>20264047</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>١٧ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٢ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1470" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1470" t="inlineStr">
@@ -54610,36 +54614,32 @@
       </c>
       <c r="G1470" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>OST-LR264772</t>
+          <t>GBLS-LR264953</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>20262152</t>
+          <t>20264430</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>٢٧ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
         <is>
-          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
-        </is>
-      </c>
-      <c r="E1471" t="inlineStr">
-        <is>
-          <t>حي المهديه</t>
-        </is>
-      </c>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr"/>
       <c r="F1471" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -54647,29 +54647,29 @@
       </c>
       <c r="G1471" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>OST-LR265023</t>
+          <t>GBLS-LR265064</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>2026613</t>
+          <t>20264519</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
         <is>
-          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1472" t="inlineStr">
@@ -54684,29 +54684,29 @@
       </c>
       <c r="G1472" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>OST-LR266524</t>
+          <t>GBLS-LR266387</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>20262767</t>
+          <t>20265632</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>١٩ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
         <is>
-          <t>خالد شاهر بن مصلح المطيري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1473" t="inlineStr">
@@ -54721,34 +54721,34 @@
       </c>
       <c r="G1473" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>OST-LR268954</t>
+          <t>GBLS-LR266569</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>20265645</t>
+          <t>20265786</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
         <is>
-          <t>مؤسسة عنوان الرفيعة للتطوير والاستثمار العقاري</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1474" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1474" t="inlineStr">
@@ -54758,108 +54758,108 @@
       </c>
       <c r="G1474" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>OST-LR269061</t>
+          <t>GBLS-LR267898</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>20265551</t>
+          <t>20267572</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١١ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
         <is>
-          <t>ناصر ظافر بن جديع ال فهاد</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1475" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1475" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1475" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>OST-LR269812</t>
+          <t>GBLS-LR268067</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>20264904</t>
+          <t>20268306</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
         <is>
-          <t>مكتب بركة عريض للعقارات</t>
+          <t>وزارة الشئون الاسلامية والدعوة والإرشاد</t>
         </is>
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1476" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1476" t="inlineStr">
         <is>
-          <t>نقل ملكية رخصة البناء</t>
+          <t>اصدار رخصة بناء حكومي</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>RUS-LR261413</t>
+          <t>OST-LR264090</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>2026629</t>
+          <t>20262152</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>٦ - ذو القعدة - ١٤٤٧ هـ</t>
+          <t>١٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
         <is>
-          <t>عبدالعزيز ناصر سعد السعد</t>
+          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
         </is>
       </c>
       <c r="E1477" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1477" t="inlineStr">
@@ -54869,34 +54869,34 @@
       </c>
       <c r="G1477" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>RUS-LR263097</t>
+          <t>OST-LR264772</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>20262566</t>
+          <t>20262152</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>٢٩ - ذو الحجة - ١٤٤٧ هـ</t>
+          <t>٢٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1478" t="inlineStr">
         <is>
-          <t>عبدالرحمن ابراهيم عبدالعزيز العريني</t>
+          <t>مؤسسة نجمه الحبونيه للمقاولات</t>
         </is>
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1478" t="inlineStr">
@@ -54906,19 +54906,19 @@
       </c>
       <c r="G1478" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>RUS-LR264967</t>
+          <t>OST-LR265023</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>2026613</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
@@ -54928,49 +54928,49 @@
       </c>
       <c r="D1479" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1479" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1479" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>RUS-LR264969</t>
+          <t>OST-LR266524</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>20262723</t>
+          <t>20262767</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
         <is>
-          <t>معدى صنيتان رازن العتيبي</t>
+          <t>خالد شاهر بن مصلح المطيري</t>
         </is>
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1480" t="inlineStr">
@@ -54980,71 +54980,71 @@
       </c>
       <c r="G1480" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>RUS-LR264980</t>
+          <t>OST-LR268954</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>20261050</t>
+          <t>20265645</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>مؤسسة عنوان الرفيعة للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1481" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1481" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>RUS-LR265038</t>
+          <t>OST-LR269061</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>2026378</t>
+          <t>20265551</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>ناصر ظافر بن جديع ال فهاد</t>
         </is>
       </c>
       <c r="E1482" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1482" t="inlineStr">
@@ -55054,34 +55054,34 @@
       </c>
       <c r="G1482" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>RUS-LR265039</t>
+          <t>OST-LR269812</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>2026817</t>
+          <t>20264904</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>مكتب بركة عريض للعقارات</t>
         </is>
       </c>
       <c r="E1483" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1483" t="inlineStr">
@@ -55091,39 +55091,39 @@
       </c>
       <c r="G1483" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>نقل ملكية رخصة البناء</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>RUS-LR265040</t>
+          <t>RUS-LR261413</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>2026379</t>
+          <t>2026629</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - ذو القعدة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>عبدالعزيز ناصر سعد السعد</t>
         </is>
       </c>
       <c r="E1484" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1484" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1484" t="inlineStr">
@@ -55135,32 +55135,32 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>RUS-LR265045</t>
+          <t>RUS-LR263097</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>20261977</t>
+          <t>20262566</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - ذو الحجة - ١٤٤٧ هـ</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
         <is>
-          <t>شركة ثرى الشراكة العقارية</t>
+          <t>عبدالرحمن ابراهيم عبدالعزيز العريني</t>
         </is>
       </c>
       <c r="E1485" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1485" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1485" t="inlineStr">
@@ -55172,27 +55172,27 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>RUS-LR265080</t>
+          <t>RUS-LR264967</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>2026902</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>١ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr">
         <is>
-          <t>محمد عبدالله محمد الحقيل</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1486" t="inlineStr">
         <is>
-          <t>حي الخزامى</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1486" t="inlineStr">
@@ -55209,22 +55209,22 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>RUS-LR265271</t>
+          <t>RUS-LR264969</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>20261204</t>
+          <t>20262723</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
         <is>
-          <t>سلطان سالم سلمان العميري</t>
+          <t>معدى صنيتان رازن العتيبي</t>
         </is>
       </c>
       <c r="E1487" t="inlineStr">
@@ -55246,32 +55246,32 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>RUS-LR265311</t>
+          <t>RUS-LR264980</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>20261011</t>
+          <t>20261050</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٩ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
         <is>
-          <t>محمد مسفر سعد البقمي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1488" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1488" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1488" t="inlineStr">
@@ -55283,27 +55283,27 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>RUS-LR265318</t>
+          <t>RUS-LR265038</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>20261025</t>
+          <t>2026378</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>٤ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
         <is>
-          <t>محمد مسفر سعد البقمي</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1489" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1489" t="inlineStr">
@@ -55320,32 +55320,32 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>RUS-LR265377</t>
+          <t>RUS-LR265039</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>20262926</t>
+          <t>2026817</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
         <is>
-          <t>شركة تأصيل العقارية</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1490" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1490" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1490" t="inlineStr">
@@ -55357,32 +55357,32 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>RUS-LR265391</t>
+          <t>RUS-LR265040</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>20263986</t>
+          <t>2026379</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>مؤسسة طالب مويس منيع المطيري للتطوير العقاري</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1491" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1491" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1491" t="inlineStr">
@@ -55394,32 +55394,32 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>RUS-LR265422</t>
+          <t>RUS-LR265045</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>20263002</t>
+          <t>20261977</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr">
         <is>
-          <t>محمد سعد محمد الوادعي</t>
+          <t>شركة ثرى الشراكة العقارية</t>
         </is>
       </c>
       <c r="E1492" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1492" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1492" t="inlineStr">
@@ -55431,32 +55431,32 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>RUS-LR265483</t>
+          <t>RUS-LR265080</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>20263669</t>
+          <t>2026902</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
         <is>
-          <t>عبدالعزيز محمد حسن العتيبي</t>
+          <t>محمد عبدالله محمد الحقيل</t>
         </is>
       </c>
       <c r="E1493" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الخزامى</t>
         </is>
       </c>
       <c r="F1493" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1493" t="inlineStr">
@@ -55468,27 +55468,27 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>RUS-LR265493</t>
+          <t>RUS-LR265271</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>20263649</t>
+          <t>20261204</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
         <is>
-          <t>وفاء عبدالله حمد المنيع</t>
+          <t>سلطان سالم سلمان العميري</t>
         </is>
       </c>
       <c r="E1494" t="inlineStr">
         <is>
-          <t>حي الزهره</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1494" t="inlineStr">
@@ -55505,32 +55505,32 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>RUS-LR265568</t>
+          <t>RUS-LR265311</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>20263528</t>
+          <t>20261011</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>محمد مسفر سعد البقمي</t>
         </is>
       </c>
       <c r="E1495" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1495" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1495" t="inlineStr">
@@ -55542,22 +55542,22 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>RUS-LR265623</t>
+          <t>RUS-LR265318</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>20261025</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>محمد مسفر سعد البقمي</t>
         </is>
       </c>
       <c r="E1496" t="inlineStr">
@@ -55567,7 +55567,7 @@
       </c>
       <c r="F1496" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1496" t="inlineStr">
@@ -55579,32 +55579,32 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>RUS-LR265625</t>
+          <t>RUS-LR265377</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>20261977</t>
+          <t>20262926</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
         <is>
-          <t>شركة ثرى الشراكة العقارية</t>
+          <t>شركة تأصيل العقارية</t>
         </is>
       </c>
       <c r="E1497" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1497" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1497" t="inlineStr">
@@ -55616,32 +55616,32 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>RUS-LR265709</t>
+          <t>RUS-LR265391</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>20261304</t>
+          <t>20263986</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
         <is>
-          <t>شركة فناء الإبتكار للتطوير العقاري</t>
+          <t>مؤسسة طالب مويس منيع المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>حي العوالي</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1498" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1498" t="inlineStr">
@@ -55653,27 +55653,27 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>RUS-LR265869</t>
+          <t>RUS-LR265422</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>20261829</t>
+          <t>20263002</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr">
         <is>
-          <t>منى محمدمساعد خالد الحكيم</t>
+          <t>محمد سعد محمد الوادعي</t>
         </is>
       </c>
       <c r="E1499" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1499" t="inlineStr">
@@ -55690,22 +55690,22 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>RUS-LR265881</t>
+          <t>RUS-LR265483</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>20262926</t>
+          <t>20263669</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
         <is>
-          <t>شركة تأصيل العقارية</t>
+          <t>عبدالعزيز محمد حسن العتيبي</t>
         </is>
       </c>
       <c r="E1500" t="inlineStr">
@@ -55715,7 +55715,7 @@
       </c>
       <c r="F1500" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1500" t="inlineStr">
@@ -55727,27 +55727,27 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>RUS-LR265941</t>
+          <t>RUS-LR265493</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>2026241</t>
+          <t>20263649</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr">
         <is>
-          <t>هلال حمدان غازي العتيبي</t>
+          <t>وفاء عبدالله حمد المنيع</t>
         </is>
       </c>
       <c r="E1501" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الزهره</t>
         </is>
       </c>
       <c r="F1501" t="inlineStr">
@@ -55764,32 +55764,32 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>RUS-LR265989</t>
+          <t>RUS-LR265568</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>20263868</t>
+          <t>20263528</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>١٣ - صفر - ١٤٤٨ هـ</t>
+          <t>٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr">
         <is>
-          <t>نايف محمد صنهات السبيعي</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1502" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1502" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1502" t="inlineStr">
@@ -55801,64 +55801,64 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>RUS-LR266100</t>
+          <t>RUS-LR265623</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>20264470</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>١٤ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr">
         <is>
-          <t>مؤسسة جدر العربية للتطوير والاستثمار العقاري</t>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
         </is>
       </c>
       <c r="E1503" t="inlineStr">
         <is>
-          <t>حي العريجاء الوسطى</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1503" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1503" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>RUS-LR266155</t>
+          <t>RUS-LR265625</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>2026379</t>
+          <t>20261977</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr">
         <is>
-          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
+          <t>شركة ثرى الشراكة العقارية</t>
         </is>
       </c>
       <c r="E1504" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1504" t="inlineStr">
@@ -55875,32 +55875,32 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>RUS-LR266384</t>
+          <t>RUS-LR265709</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>20264824</t>
+          <t>20261304</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>١٩ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
-          <t>عبدالحكيم علي عبده محمد الحكمي</t>
+          <t>شركة فناء الإبتكار للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1505" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1505" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1505" t="inlineStr">
@@ -55912,27 +55912,27 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>RUS-LR266540</t>
+          <t>RUS-LR265869</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>20261645</t>
+          <t>20261829</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>٢١ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>مؤسسة مباني الورود للتطوير العقاري</t>
+          <t>منى محمدمساعد خالد الحكيم</t>
         </is>
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1506" t="inlineStr">
@@ -55949,32 +55949,32 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>RUS-LR266691</t>
+          <t>RUS-LR265881</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>202517</t>
+          <t>20262926</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>٢٣ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr">
         <is>
-          <t>ماجد بن عبدالله نابت الشهراني</t>
+          <t>شركة تأصيل العقارية</t>
         </is>
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1507" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1507" t="inlineStr">
@@ -55986,32 +55986,32 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>RUS-LR266771</t>
+          <t>RUS-LR265941</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>20262626</t>
+          <t>2026241</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1508" t="inlineStr">
         <is>
-          <t>بزيع سليمان بزيع المبارك</t>
+          <t>هلال حمدان غازي العتيبي</t>
         </is>
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1508" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1508" t="inlineStr">
@@ -56023,27 +56023,27 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>RUS-LR266803</t>
+          <t>RUS-LR265989</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>20264988</t>
+          <t>20263868</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٣ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr">
         <is>
-          <t>سلطان بن منير بن منيف البقمي</t>
+          <t>نايف محمد صنهات السبيعي</t>
         </is>
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1509" t="inlineStr">
@@ -56060,27 +56060,27 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>RUS-LR266814</t>
+          <t>RUS-LR266100</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>2026605</t>
+          <t>20264470</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٤ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr">
         <is>
-          <t>مؤسسة فهد سعود اليوسف</t>
+          <t>مؤسسة جدر العربية للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي العريجاء الوسطى</t>
         </is>
       </c>
       <c r="F1510" t="inlineStr">
@@ -56090,34 +56090,34 @@
       </c>
       <c r="G1510" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>RUS-LR266930</t>
+          <t>RUS-LR266155</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>20265106</t>
+          <t>2026379</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>عبدالهادي جعفر خنثل بن شري</t>
+          <t>مؤسسة فخامة المنزل للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1511" t="inlineStr">
@@ -56134,27 +56134,27 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>RUS-LR266984</t>
+          <t>RUS-LR266384</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>2026902</t>
+          <t>20264824</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>١٩ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>محمد عبدالله محمد الحقيل</t>
+          <t>عبدالحكيم علي عبده محمد الحكمي</t>
         </is>
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>حي الخزامى</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1512" t="inlineStr">
@@ -56164,34 +56164,34 @@
       </c>
       <c r="G1512" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>RUS-LR266991</t>
+          <t>RUS-LR266540</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>20265006</t>
+          <t>20261645</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢١ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>شركة وتد الديار</t>
+          <t>مؤسسة مباني الورود للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1513" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1513" t="inlineStr">
@@ -56208,27 +56208,27 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>RUS-LR266993</t>
+          <t>RUS-LR266691</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>20265012</t>
+          <t>202517</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٣ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
-          <t>شركة وتد الديار</t>
+          <t>ماجد بن عبدالله نابت الشهراني</t>
         </is>
       </c>
       <c r="E1514" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1514" t="inlineStr">
@@ -56245,22 +56245,22 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>RUS-LR267452</t>
+          <t>RUS-LR266771</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>2026865</t>
+          <t>20262626</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+          <t>بزيع سليمان بزيع المبارك</t>
         </is>
       </c>
       <c r="E1515" t="inlineStr">
@@ -56270,7 +56270,7 @@
       </c>
       <c r="F1515" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1515" t="inlineStr">
@@ -56282,27 +56282,27 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>RUS-LR267541</t>
+          <t>RUS-LR266803</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>20263700</t>
+          <t>20264988</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>مؤسسة نرجس المبانى للتطوير العقاري</t>
+          <t>سلطان بن منير بن منيف البقمي</t>
         </is>
       </c>
       <c r="E1516" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1516" t="inlineStr">
@@ -56319,27 +56319,27 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>RUS-LR267556</t>
+          <t>RUS-LR266814</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>20263440</t>
+          <t>2026605</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>ابراهيم فائز ابراهيم القحطاني</t>
+          <t>مؤسسة فهد سعود اليوسف</t>
         </is>
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1517" t="inlineStr">
@@ -56356,27 +56356,27 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>RUS-LR267632</t>
+          <t>RUS-LR266930</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>2026613</t>
+          <t>20265106</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
+          <t>عبدالهادي جعفر خنثل بن شري</t>
         </is>
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1518" t="inlineStr">
@@ -56393,25 +56393,29 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>RUS-LR267647</t>
+          <t>RUS-LR266984</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>20264482</t>
+          <t>2026902</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>عناد عاتق عيد العميرى</t>
-        </is>
-      </c>
-      <c r="E1519" t="inlineStr"/>
+          <t>محمد عبدالله محمد الحقيل</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>حي الخزامى</t>
+        </is>
+      </c>
       <c r="F1519" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56419,34 +56423,34 @@
       </c>
       <c r="G1519" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>RUS-LR267651</t>
+          <t>RUS-LR266991</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>20262551</t>
+          <t>20265006</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>عناد عاتق عيد العميرى</t>
+          <t>شركة وتد الديار</t>
         </is>
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1520" t="inlineStr">
@@ -56463,27 +56467,27 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>RUS-LR267722</t>
+          <t>RUS-LR266993</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>20264896</t>
+          <t>20265012</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>عبدالعزيز بن على بن سمران الحربي</t>
+          <t>شركة وتد الديار</t>
         </is>
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1521" t="inlineStr">
@@ -56500,25 +56504,29 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>RUS-LR267741</t>
+          <t>RUS-LR267452</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>20264382</t>
+          <t>2026865</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>عبدالرحمن سعود محمد الخريف</t>
-        </is>
-      </c>
-      <c r="E1522" t="inlineStr"/>
+          <t>مؤسسة تميز الفرسان للتطوير والاستثمار العقاري</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
       <c r="F1522" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56533,27 +56541,27 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>RUS-LR267767</t>
+          <t>RUS-LR267541</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>202648</t>
+          <t>20263700</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>خالد عبدالرحمن حمدان السبيعي</t>
+          <t>مؤسسة نرجس المبانى للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1523" t="inlineStr">
@@ -56570,27 +56578,27 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>RUS-LR268079</t>
+          <t>RUS-LR267556</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>2026394</t>
+          <t>20263440</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>ابراهيم فائز ابراهيم القحطاني</t>
         </is>
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1524" t="inlineStr">
@@ -56607,27 +56615,27 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>RUS-LR268340</t>
+          <t>RUS-LR267632</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>20264221</t>
+          <t>2026613</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>بدر محمد بن حثيري البقمي</t>
+          <t>مؤسسة راجح عليثه عباد المطيري للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1525" t="inlineStr">
@@ -56644,29 +56652,25 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>RUS-LR268470</t>
+          <t>RUS-LR267647</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>20261779</t>
+          <t>20264482</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr">
         <is>
-          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>مؤسسة التطوير النموذجية للتطوير العقاري</t>
-        </is>
-      </c>
-      <c r="E1526" t="inlineStr">
-        <is>
-          <t>حي ظهره لبن</t>
-        </is>
-      </c>
+          <t>عناد عاتق عيد العميرى</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr"/>
       <c r="F1526" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56681,22 +56685,22 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>RUS-LR268532</t>
+          <t>RUS-LR267651</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>2026394</t>
+          <t>20262551</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>عناد عاتق عيد العميرى</t>
         </is>
       </c>
       <c r="E1527" t="inlineStr">
@@ -56718,66 +56722,62 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>RUS-LR268621</t>
+          <t>RUS-LR267722</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>20263528</t>
+          <t>20264896</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr">
         <is>
-          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1528" t="inlineStr">
         <is>
-          <t>مؤسسة نخبة التطور العقارية</t>
+          <t>عبدالعزيز بن على بن سمران الحربي</t>
         </is>
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1528" t="inlineStr">
         <is>
-          <t>مرفوض</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1528" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>RUS-LR268843</t>
+          <t>RUS-LR267741</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>20266365</t>
+          <t>20264382</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>خالد بن سعد بن سعود العصيمي</t>
-        </is>
-      </c>
-      <c r="E1529" t="inlineStr">
-        <is>
-          <t>حي العريجاء الغربي</t>
-        </is>
-      </c>
+          <t>عبدالرحمن سعود محمد الخريف</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr"/>
       <c r="F1529" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56792,25 +56792,29 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>RUS-LR268863</t>
+          <t>RUS-LR267767</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>20264382</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>عبدالرحمن سعود محمد الخريف</t>
-        </is>
-      </c>
-      <c r="E1530" t="inlineStr"/>
+          <t>خالد عبدالرحمن حمدان السبيعي</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>حي ضاحية نمار</t>
+        </is>
+      </c>
       <c r="F1530" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -56825,32 +56829,32 @@
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>RUS-LR268896</t>
+          <t>RUS-LR268079</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>20261892</t>
+          <t>2026394</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>عبدالله ابن علي ابن شايع ال شفلوت</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1531" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1531" t="inlineStr">
@@ -56862,27 +56866,27 @@
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>RUS-LR268922</t>
+          <t>RUS-LR268340</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>2026916</t>
+          <t>20264221</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>علي عائض بن علي البقمي</t>
+          <t>بدر محمد بن حثيري البقمي</t>
         </is>
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1532" t="inlineStr">
@@ -56899,27 +56903,27 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>RUS-LR269043</t>
+          <t>RUS-LR268470</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>20266122</t>
+          <t>20261779</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
+          <t>مؤسسة التطوير النموذجية للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1533" t="inlineStr">
@@ -56936,17 +56940,17 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>RUS-LR269055</t>
+          <t>RUS-LR268532</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>20263495</t>
+          <t>2026394</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٨ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
@@ -56973,69 +56977,69 @@
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>RUS-LR269087</t>
+          <t>RUS-LR268621</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>20266955</t>
+          <t>20263528</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
         <is>
-          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>نواف عبدالله حسين القحطاني</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1535" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مرفوض</t>
         </is>
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>RUS-LR269169</t>
+          <t>RUS-LR268843</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>20266137</t>
+          <t>20266365</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>شركة رصين نجد العقارية</t>
+          <t>خالد بن سعد بن سعود العصيمي</t>
         </is>
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1536" t="inlineStr">
         <is>
-          <t>ملغي</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1536" t="inlineStr">
@@ -57047,29 +57051,25 @@
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>RUS-LR269180</t>
+          <t>RUS-LR268863</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>20262394</t>
+          <t>20264382</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>محمد عبدالوهاب سلوم السلوم</t>
-        </is>
-      </c>
-      <c r="E1537" t="inlineStr">
-        <is>
-          <t>حي نمار</t>
-        </is>
-      </c>
+          <t>عبدالرحمن سعود محمد الخريف</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr"/>
       <c r="F1537" t="inlineStr">
         <is>
           <t>مكتمل</t>
@@ -57084,27 +57084,27 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>RUS-LR269184</t>
+          <t>RUS-LR268896</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>2026734</t>
+          <t>20261892</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٣ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>مؤسسة عبدالعزيز بن جلوي بن محارب المطيري</t>
+          <t>عبدالله ابن علي ابن شايع ال شفلوت</t>
         </is>
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
@@ -57121,27 +57121,27 @@
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>RUS-LR269207</t>
+          <t>RUS-LR268922</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>20263023</t>
+          <t>2026916</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>عائض عبدالله مبارك القحطاني</t>
+          <t>علي عائض بن علي البقمي</t>
         </is>
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1539" t="inlineStr">
@@ -57151,34 +57151,34 @@
       </c>
       <c r="G1539" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>RUS-LR269208</t>
+          <t>RUS-LR269043</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>20263021</t>
+          <t>20266122</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>عائض عبدالله مبارك القحطاني</t>
+          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
         </is>
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1540" t="inlineStr">
@@ -57188,34 +57188,34 @@
       </c>
       <c r="G1540" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>RUS-LR269243</t>
+          <t>RUS-LR269055</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>20266137</t>
+          <t>20263495</t>
         </is>
       </c>
       <c r="C1541" t="inlineStr">
         <is>
-          <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>شركة رصين نجد العقارية</t>
+          <t>مؤسسة نخبة التطور العقارية</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>حي الحزم</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
@@ -57232,32 +57232,32 @@
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>RUS-LR269411</t>
+          <t>RUS-LR269087</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>20267329</t>
+          <t>20266955</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٥ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1542" t="inlineStr">
         <is>
-          <t>مؤسسة مجد الوفاء للتطوير العقاري</t>
+          <t>نواف عبدالله حسين القحطاني</t>
         </is>
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1542" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1542" t="inlineStr">
@@ -57269,32 +57269,32 @@
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>RUS-LR269523</t>
+          <t>RUS-LR269169</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>20263699</t>
+          <t>20266137</t>
         </is>
       </c>
       <c r="C1543" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1543" t="inlineStr">
         <is>
-          <t>مسعود حسن بن قبحان الغامدي</t>
+          <t>شركة رصين نجد العقارية</t>
         </is>
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1543" t="inlineStr">
         <is>
-          <t>قيد العمل - المهندس</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1543" t="inlineStr">
@@ -57306,59 +57306,59 @@
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>RUS-LR269592</t>
+          <t>RUS-LR269180</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>20262178</t>
+          <t>20262394</t>
         </is>
       </c>
       <c r="C1544" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
-          <t>شركة إثراء الرياض العقارية</t>
+          <t>محمد عبدالوهاب سلوم السلوم</t>
         </is>
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>حي العوالي</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1544" t="inlineStr">
         <is>
-          <t>ملغي</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1544" t="inlineStr">
         <is>
-          <t>تجديد وتعديل رخصة بناء</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>RUS-LR269603</t>
+          <t>RUS-LR269184</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>20264202</t>
+          <t>2026734</t>
         </is>
       </c>
       <c r="C1545" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t>جابر علي احمد مجرشي</t>
+          <t>مؤسسة عبدالعزيز بن جلوي بن محارب المطيري</t>
         </is>
       </c>
       <c r="E1545" t="inlineStr">
@@ -57368,7 +57368,7 @@
       </c>
       <c r="F1545" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1545" t="inlineStr">
@@ -57380,101 +57380,101 @@
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>RUS-LR269641</t>
+          <t>RUS-LR269207</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>20263967</t>
+          <t>20263023</t>
         </is>
       </c>
       <c r="C1546" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>عبدالكريم دخيل الله خاتم السلمي</t>
+          <t>عائض عبدالله مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1546" t="inlineStr">
         <is>
-          <t>استكمال التعديلات</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1546" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>RUS-LR269644</t>
+          <t>RUS-LR269208</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>20261830</t>
+          <t>20263021</t>
         </is>
       </c>
       <c r="C1547" t="inlineStr">
         <is>
-          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>٢٦ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>مؤسسة ارض وسكن للتطوير العقاري</t>
+          <t>عائض عبدالله مبارك القحطاني</t>
         </is>
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1547" t="inlineStr">
         <is>
-          <t>قيد العمل - مشرف رخص البناء</t>
+          <t>مكتمل</t>
         </is>
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>تعديل رخصة بناء</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>SIP-LR264068</t>
+          <t>RUS-LR269243</t>
         </is>
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>20263876</t>
+          <t>20266137</t>
         </is>
       </c>
       <c r="C1548" t="inlineStr">
         <is>
-          <t>١٧ - محرم - ١٤٤٨ هـ</t>
+          <t>٢٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>نوره عبدالعزيز محمد العريفي</t>
+          <t>شركة رصين نجد العقارية</t>
         </is>
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي الحزم</t>
         </is>
       </c>
       <c r="F1548" t="inlineStr">
@@ -57484,34 +57484,34 @@
       </c>
       <c r="G1548" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>SIP-LR264320</t>
+          <t>RUS-LR269411</t>
         </is>
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>20264534</t>
+          <t>20267329</t>
         </is>
       </c>
       <c r="C1549" t="inlineStr">
         <is>
-          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
+          <t>١ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1549" t="inlineStr">
         <is>
-          <t>شركة مدماك الغد العقارية</t>
+          <t>مؤسسة مجد الوفاء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1549" t="inlineStr">
@@ -57521,108 +57521,108 @@
       </c>
       <c r="G1549" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>SIP-LR264372</t>
+          <t>RUS-LR269523</t>
         </is>
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>20263907</t>
+          <t>20263699</t>
         </is>
       </c>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>٢١ - محرم - ١٤٤٨ هـ</t>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
+          <t>مسعود حسن بن قبحان الغامدي</t>
         </is>
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>حي شبرا</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1550" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>قيد العمل - المهندس</t>
         </is>
       </c>
       <c r="G1550" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>SIP-LR265231</t>
+          <t>RUS-LR269592</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>20264645</t>
+          <t>20262178</t>
         </is>
       </c>
       <c r="C1551" t="inlineStr">
         <is>
-          <t>٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>علي بن محمد بن مسفر الحلافي</t>
+          <t>شركة إثراء الرياض العقارية</t>
         </is>
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي العوالي</t>
         </is>
       </c>
       <c r="F1551" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>ملغي</t>
         </is>
       </c>
       <c r="G1551" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تجديد وتعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>SIP-LR265499</t>
+          <t>RUS-LR269603</t>
         </is>
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>20264866</t>
+          <t>20264202</t>
         </is>
       </c>
       <c r="C1552" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>شركة المسكن الأمثل للتطوير والاستثمار العقاري</t>
+          <t>جابر علي احمد مجرشي</t>
         </is>
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1552" t="inlineStr">
@@ -57632,71 +57632,71 @@
       </c>
       <c r="G1552" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>SIP-LR265502</t>
+          <t>RUS-LR269641</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>20264858</t>
+          <t>20263967</t>
         </is>
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>٦ - صفر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>سلطان ناصر زيد بن شنار</t>
+          <t>عبدالكريم دخيل الله خاتم السلمي</t>
         </is>
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1553" t="inlineStr">
         <is>
-          <t>مكتمل</t>
+          <t>استكمال التعديلات</t>
         </is>
       </c>
       <c r="G1553" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>SIP-LR265662</t>
+          <t>RUS-LR269644</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>20264983</t>
+          <t>20261830</t>
         </is>
       </c>
       <c r="C1554" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٣ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>عمر ابن عبدالعزيز ابن عبدالله الغامدي</t>
+          <t>مؤسسة ارض وسكن للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>حي العريجاء الغربي</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1554" t="inlineStr">
@@ -57706,34 +57706,34 @@
       </c>
       <c r="G1554" t="inlineStr">
         <is>
-          <t>تجهيز موقع</t>
+          <t>تعديل رخصة بناء</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>SIP-LR265713</t>
+          <t>SIP-LR264068</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>20265038</t>
+          <t>20263876</t>
         </is>
       </c>
       <c r="C1555" t="inlineStr">
         <is>
-          <t>٨ - صفر - ١٤٤٨ هـ</t>
+          <t>١٧ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>فهده سفر بهيشان الحافي</t>
+          <t>نوره عبدالعزيز محمد العريفي</t>
         </is>
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>حي ضاحية نمار</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1555" t="inlineStr">
@@ -57750,27 +57750,27 @@
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>SIP-LR265893</t>
+          <t>SIP-LR264320</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>20265178</t>
+          <t>20264534</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
         <is>
-          <t>١٢ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>مؤسسة محمد علي محمد التميمي للتطوير العقاري</t>
+          <t>شركة مدماك الغد العقارية</t>
         </is>
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1556" t="inlineStr">
@@ -57787,27 +57787,27 @@
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>SIP-LR266235</t>
+          <t>SIP-LR264372</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>20265492</t>
+          <t>20263907</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢١ - محرم - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>مؤسسة بصمة ثري للمقاولات المعمارية</t>
         </is>
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي شبرا</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -57824,27 +57824,27 @@
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>SIP-LR266237</t>
+          <t>SIP-LR265231</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>20265494</t>
+          <t>20264645</t>
         </is>
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>علي بن محمد بن مسفر الحلافي</t>
         </is>
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1558" t="inlineStr">
@@ -57861,27 +57861,27 @@
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>SIP-LR266243</t>
+          <t>SIP-LR265499</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>20265495</t>
+          <t>20264866</t>
         </is>
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>١٥ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
+          <t>شركة المسكن الأمثل للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي السويدي الغربي</t>
         </is>
       </c>
       <c r="F1559" t="inlineStr">
@@ -57898,27 +57898,27 @@
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>SIP-LR266356</t>
+          <t>SIP-LR265502</t>
         </is>
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>20265660</t>
+          <t>20264858</t>
         </is>
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>١٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٦ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>شركة امثل للاستثمار</t>
+          <t>سلطان ناصر زيد بن شنار</t>
         </is>
       </c>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1560" t="inlineStr">
@@ -57935,27 +57935,27 @@
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>SIP-LR266526</t>
+          <t>SIP-LR265662</t>
         </is>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>20265751</t>
+          <t>20264983</t>
         </is>
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+          <t>عمر ابن عبدالعزيز ابن عبدالله الغامدي</t>
         </is>
       </c>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي العريجاء الغربي</t>
         </is>
       </c>
       <c r="F1561" t="inlineStr">
@@ -57972,27 +57972,27 @@
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>SIP-LR266527</t>
+          <t>SIP-LR265713</t>
         </is>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>20265752</t>
+          <t>20265038</t>
         </is>
       </c>
       <c r="C1562" t="inlineStr">
         <is>
-          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
+          <t>٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
+          <t>فهده سفر بهيشان الحافي</t>
         </is>
       </c>
       <c r="E1562" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ضاحية نمار</t>
         </is>
       </c>
       <c r="F1562" t="inlineStr">
@@ -58009,27 +58009,27 @@
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>SIP-LR266637</t>
+          <t>SIP-LR265893</t>
         </is>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>20265853</t>
+          <t>20265178</t>
         </is>
       </c>
       <c r="C1563" t="inlineStr">
         <is>
-          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+          <t>١٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>حنان عبدالرحيم مطلق الاحمدي</t>
+          <t>مؤسسة محمد علي محمد التميمي للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1563" t="inlineStr">
@@ -58046,27 +58046,27 @@
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>SIP-LR266649</t>
+          <t>SIP-LR266235</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>20265864</t>
+          <t>20265492</t>
         </is>
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>مؤسسة الوجهة الحديثة للتطوير العقاري</t>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1564" t="inlineStr">
@@ -58083,27 +58083,27 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>SIP-LR266788</t>
+          <t>SIP-LR266237</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>20265977</t>
+          <t>20265494</t>
         </is>
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>عبدالعزيز مقعد مرزوق المطيري</t>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1565" t="inlineStr">
@@ -58120,27 +58120,27 @@
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>SIP-LR266976</t>
+          <t>SIP-LR266243</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>20266673</t>
+          <t>20265495</t>
         </is>
       </c>
       <c r="C1566" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>١٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>عبيد محمد مطلق العصيمي</t>
+          <t>مؤسسة عمل متن البناء للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1566" t="inlineStr">
@@ -58157,27 +58157,27 @@
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>SIP-LR266985</t>
+          <t>SIP-LR266356</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>20266172</t>
+          <t>20265660</t>
         </is>
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
+          <t>١٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>شركة ساف العقارية</t>
+          <t>شركة امثل للاستثمار</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي ظهره لبن</t>
         </is>
       </c>
       <c r="F1567" t="inlineStr">
@@ -58194,27 +58194,27 @@
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>SIP-LR267002</t>
+          <t>SIP-LR266526</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>20266182</t>
+          <t>20265751</t>
         </is>
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>٢٨ - صفر - ١٤٤٨ هـ</t>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>شركة ساف العقارية</t>
+          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>حي نمار</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1568" t="inlineStr">
@@ -58231,22 +58231,22 @@
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>SIP-LR267466</t>
+          <t>SIP-LR266527</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>20266601</t>
+          <t>20265752</t>
         </is>
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٠ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>شركة عمرانيات الجزيره للمقاولات</t>
+          <t>شركة رسن التقدم للتطوير والاستثمار العقاري</t>
         </is>
       </c>
       <c r="E1569" t="inlineStr">
@@ -58268,27 +58268,27 @@
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>SIP-LR267636</t>
+          <t>SIP-LR266637</t>
         </is>
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>20266785</t>
+          <t>20265853</t>
         </is>
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>شركة المسمات للتطوير والاستثمار العقاري شخص واحد</t>
+          <t>حنان عبدالرحيم مطلق الاحمدي</t>
         </is>
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>حي لبن</t>
+          <t>حي عرقه</t>
         </is>
       </c>
       <c r="F1570" t="inlineStr">
@@ -58305,27 +58305,27 @@
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>SIP-LR267770</t>
+          <t>SIP-LR266649</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>20266879</t>
+          <t>20265864</t>
         </is>
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٢ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>مؤسسة الوجهة الحديثة للتطوير العقاري</t>
         </is>
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1571" t="inlineStr">
@@ -58342,27 +58342,27 @@
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>SIP-LR267774</t>
+          <t>SIP-LR266788</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>20266887</t>
+          <t>20265977</t>
         </is>
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٥ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>عبدالعزيز مقعد مرزوق المطيري</t>
         </is>
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1572" t="inlineStr">
@@ -58379,27 +58379,27 @@
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>SIP-LR267777</t>
+          <t>SIP-LR266976</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>20266896</t>
+          <t>20266673</t>
         </is>
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>شركة حلول التطوير العقارية</t>
+          <t>عبيد محمد مطلق العصيمي</t>
         </is>
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي طويق</t>
         </is>
       </c>
       <c r="F1573" t="inlineStr">
@@ -58416,27 +58416,27 @@
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>SIP-LR267816</t>
+          <t>SIP-LR266985</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>20266926</t>
+          <t>20266172</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٧ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>عبدالعزيز غيث موسى الغيث</t>
+          <t>شركة ساف العقارية</t>
         </is>
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>حي طويق</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1574" t="inlineStr">
@@ -58453,27 +58453,27 @@
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>SIP-LR267818</t>
+          <t>SIP-LR267002</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>20266927</t>
+          <t>20266182</t>
         </is>
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٢٨ - صفر - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+          <t>شركة ساف العقارية</t>
         </is>
       </c>
       <c r="E1575" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي نمار</t>
         </is>
       </c>
       <c r="F1575" t="inlineStr">
@@ -58490,27 +58490,27 @@
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>SIP-LR268065</t>
+          <t>SIP-LR267466</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>20267343</t>
+          <t>20266601</t>
         </is>
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٤ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>عبدالعزيز صالح مبارك الماجد</t>
+          <t>شركة عمرانيات الجزيره للمقاولات</t>
         </is>
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>حي ديراب</t>
+          <t>حي المهديه</t>
         </is>
       </c>
       <c r="F1576" t="inlineStr">
@@ -58527,27 +58527,27 @@
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>SIP-LR268337</t>
+          <t>SIP-LR267636</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>20267375</t>
+          <t>20266785</t>
         </is>
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>٧ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>شركة الأماني العقارية (شركة شخص واحد)</t>
+          <t>شركة المسمات للتطوير والاستثمار العقاري شخص واحد</t>
         </is>
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>حي السويدي الغربي</t>
+          <t>حي لبن</t>
         </is>
       </c>
       <c r="F1577" t="inlineStr">
@@ -58564,27 +58564,27 @@
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>SIP-LR268611</t>
+          <t>SIP-LR267770</t>
         </is>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>20267740</t>
+          <t>20266879</t>
         </is>
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>مؤسسة أوكن للتطوير العقاري</t>
+          <t>شركة حلول التطوير العقارية</t>
         </is>
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>حي ظهره لبن</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1578" t="inlineStr">
@@ -58601,27 +58601,27 @@
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>SIP-LR269370</t>
+          <t>SIP-LR267774</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>20268256</t>
+          <t>20266887</t>
         </is>
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>محمد حمد عثمان الحسين</t>
+          <t>شركة حلول التطوير العقارية</t>
         </is>
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>حي عرقه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1579" t="inlineStr">
@@ -58638,27 +58638,27 @@
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>SIP-LR269536</t>
+          <t>SIP-LR267777</t>
         </is>
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>20268409</t>
+          <t>20266896</t>
         </is>
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+          <t>شركة حلول التطوير العقارية</t>
         </is>
       </c>
       <c r="E1580" t="inlineStr">
         <is>
-          <t>حي المهديه</t>
+          <t>حي ديراب</t>
         </is>
       </c>
       <c r="F1580" t="inlineStr">
@@ -58675,35 +58675,294 @@
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
+          <t>SIP-LR267816</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>20266926</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>عبدالعزيز غيث موسى الغيث</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>حي طويق</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>SIP-LR267818</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>20266927</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>١٠ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>SIP-LR268065</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>20267343</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>١٣ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>عبدالعزيز صالح مبارك الماجد</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>حي ديراب</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>SIP-LR268337</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>20267375</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>١٧ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>شركة الأماني العقارية (شركة شخص واحد)</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>حي السويدي الغربي</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>SIP-LR268611</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>20267740</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>١٩ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>مؤسسة أوكن للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>حي ظهره لبن</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>SIP-LR269370</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>20268256</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>٢٨ - ربيع الأول - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>محمد حمد عثمان الحسين</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>حي عرقه</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>SIP-LR269536</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>20268409</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>٢ - ربيع الآخر - ١٤٤٨ هـ</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>مؤسسة وضاح داود سلمان القحطاني للتطوير العقاري</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>حي المهديه</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>تجهيز موقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
           <t>SIP-LR269720</t>
         </is>
       </c>
-      <c r="B1581" t="inlineStr">
+      <c r="B1588" t="inlineStr">
         <is>
           <t>20268540</t>
         </is>
       </c>
-      <c r="C1581" t="inlineStr">
+      <c r="C1588" t="inlineStr">
         <is>
           <t>٤ - ربيع الآخر - ١٤٤٨ هـ</t>
         </is>
       </c>
-      <c r="D1581" t="inlineStr">
+      <c r="D1588" t="inlineStr">
         <is>
           <t>مؤسسة عوالي الابداع للمقاولات</t>
         </is>
       </c>
-      <c r="E1581" t="inlineStr">
+      <c r="E1588" t="inlineStr">
         <is>
           <t>حي العوالي</t>
         </is>
       </c>
-      <c r="F1581" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="G1581" t="inlineStr">
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr">
         <is>
           <t>تجهيز موقع</t>
         </is>
